--- a/tame_output/ON/bt/strategyON_20240711.xlsx
+++ b/tame_output/ON/bt/strategyON_20240711.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-500.5%</t>
+          <t>-500.6%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -48034,16 +48034,16 @@
         <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.389748628475305</v>
+        <v>-3.389835814827719</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.213719204070482</v>
+        <v>2.213684329529515</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6910641881146473</v>
+        <v>0.6911839319548028</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.984613592643139</v>
+        <v>3.984685438947232</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240711.xlsx
+++ b/tame_output/ON/bt/strategyON_20240711.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>35.6%</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.8%</t>
+          <t>-66.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-500.6%</t>
+          <t>-501.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-154.9%</t>
+          <t>-164.8%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-125.6%</t>
+          <t>-125.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-154.9%</t>
+          <t>-155.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-57.4%</t>
         </is>
       </c>
     </row>
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.584804573565458</v>
+        <v>2.487261445495994</v>
       </c>
       <c r="D1967" t="n">
         <v>-3.47612718431148</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.193997275527119</v>
+        <v>1.096454147457655</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3303187745317229</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.782995838284492</v>
+        <v>2.685452710215028</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.585466921957117</v>
+        <v>2.487923793887653</v>
       </c>
       <c r="D1968" t="n">
         <v>-3.469974478258695</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.197120706339891</v>
+        <v>1.099577578270427</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3364714805845072</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.787349810307821</v>
+        <v>2.689806682238357</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.584547398697227</v>
+        <v>2.487004270627763</v>
       </c>
       <c r="D1969" t="n">
         <v>-3.486783776409197</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.189477463819801</v>
+        <v>1.091934335750337</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3196621824340056</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.776344708157631</v>
+        <v>2.678801580088167</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.650882952494048</v>
+        <v>2.553339824424584</v>
       </c>
       <c r="D1970" t="n">
         <v>-3.424485777633075</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.280732217127071</v>
+        <v>1.183189089057607</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3196621824340056</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.842680261954452</v>
+        <v>2.745137133884988</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.453174954208175</v>
+        <v>2.355631826138711</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.222695579967917</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.163740297907261</v>
+        <v>1.066197169837797</v>
       </c>
       <c r="F1971" t="n">
         <v>0.51768037460316</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.763783178970071</v>
+        <v>2.666240050900607</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.52346518653035</v>
+        <v>2.425922058460886</v>
       </c>
       <c r="D1972" t="n">
         <v>-3.149317482879181</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.263381769064931</v>
+        <v>1.165838640995467</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5910584716918965</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.878100269545488</v>
+        <v>2.780557141476025</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.538092922646394</v>
+        <v>2.44054979457693</v>
       </c>
       <c r="D1973" t="n">
         <v>-3.247058027504155</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.238913287330984</v>
+        <v>1.141370159261521</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5751691935589163</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.883194438781744</v>
+        <v>2.78565131071228</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.536628903471065</v>
+        <v>2.439085775401602</v>
       </c>
       <c r="D1974" t="n">
         <v>-3.423395787627084</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.166914164106484</v>
+        <v>1.069371036037021</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3988314334359869</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.775927763532658</v>
+        <v>2.678384635463194</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.535120521510994</v>
+        <v>2.43757739344153</v>
       </c>
       <c r="D1975" t="n">
         <v>-3.346973741195157</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.195974600719184</v>
+        <v>1.09843147264972</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3988314334359869</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.774419381572586</v>
+        <v>2.676876253503123</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.53498338894643</v>
+        <v>2.437440260876966</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.302600609556589</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.213586720810047</v>
+        <v>1.116043592740584</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4432045650745555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.800906127991164</v>
+        <v>2.7033629999217</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.529377183085021</v>
+        <v>2.431834055015557</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.179766388669421</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.257114203303505</v>
+        <v>1.159571075234041</v>
       </c>
       <c r="F1977" t="n">
         <v>0.4432045650745555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.795299922129754</v>
+        <v>2.69775679406029</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.535758940112825</v>
+        <v>2.438215812043361</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.132110658108366</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.282558252555732</v>
+        <v>1.185015124486267</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4908602956356112</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.830275117494192</v>
+        <v>2.732731989424728</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.54065131348755</v>
+        <v>2.443108185418086</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.031592499609611</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.327657889329958</v>
+        <v>1.230114761260494</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5913784541343657</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.89547838596817</v>
+        <v>2.797935257898705</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.527405985963422</v>
+        <v>2.429862857893958</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.092259090012</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.290145925644875</v>
+        <v>1.192602797575411</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5096801374158321</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.833214068412922</v>
+        <v>2.735670940343458</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.531503688574051</v>
+        <v>2.433960560504587</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.047420688403602</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.312178988898863</v>
+        <v>1.214635860829398</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5142235703607015</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.840037830790472</v>
+        <v>2.742494702721008</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.535664628205129</v>
+        <v>2.438121500135665</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.148179324160601</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.276036474227141</v>
+        <v>1.178493346157677</v>
       </c>
       <c r="F1982" t="n">
         <v>0.4253980016336961</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.790903429185347</v>
+        <v>2.693360301115883</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.541544230732966</v>
+        <v>2.444001102663502</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.1039764870747</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.299597211589339</v>
+        <v>1.202054083519874</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4696008387195966</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.823304733964724</v>
+        <v>2.72576160589526</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.539954231202214</v>
+        <v>2.442411103132749</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.140955514738144</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.283215600993209</v>
+        <v>1.185672472923745</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5065747405109271</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.84389907550877</v>
+        <v>2.746355947439306</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.591201996385253</v>
+        <v>2.493658868315789</v>
       </c>
       <c r="D1985" t="n">
         <v>-2.982664097198871</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.397779933191958</v>
+        <v>1.300236805122493</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5065747405109271</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.89514684069181</v>
+        <v>2.797603712622346</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.589642700979506</v>
+        <v>2.492099572910042</v>
       </c>
       <c r="D1986" t="n">
         <v>-2.775022093564395</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.479277439240001</v>
+        <v>1.381734311170537</v>
       </c>
       <c r="F1986" t="n">
         <v>0.7142167441454033</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.018172747466749</v>
+        <v>2.920629619397284</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.584590929217776</v>
+        <v>2.487047801148312</v>
       </c>
       <c r="D1987" t="n">
         <v>-2.723990000841867</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.494638504567282</v>
+        <v>1.397095376497818</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7652488368679312</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.043740231338536</v>
+        <v>2.946197103269071</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.601778333310481</v>
+        <v>2.504235205241017</v>
       </c>
       <c r="D1988" t="n">
         <v>-2.658765819714661</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.53791558111087</v>
+        <v>1.440372453041405</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8304730179951368</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.100062144107564</v>
+        <v>3.002519016038099</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.597739305609762</v>
+        <v>2.500196177540297</v>
       </c>
       <c r="D1989" t="n">
         <v>-2.621338799643528</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.548847361438604</v>
+        <v>1.451304233369139</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8357245560243185</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.099174039224353</v>
+        <v>3.001630911154889</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.598996097941002</v>
+        <v>2.501452969871538</v>
       </c>
       <c r="D1990" t="n">
         <v>-2.641450455678236</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.54205949135596</v>
+        <v>1.444516363286496</v>
       </c>
       <c r="F1990" t="n">
         <v>0.8467519010217377</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.107047238554045</v>
+        <v>3.009504110484581</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.759553868962213</v>
+        <v>2.662010740892748</v>
       </c>
       <c r="D1991" t="n">
         <v>-2.587705641251031</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.724115188148053</v>
+        <v>1.626572060078589</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8568152104621997</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.273642995239533</v>
+        <v>3.176099867170068</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.87966677818003</v>
+        <v>2.782123650110566</v>
       </c>
       <c r="D1992" t="n">
         <v>-2.563914072644889</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.853744724808327</v>
+        <v>1.756201596738863</v>
       </c>
       <c r="F1992" t="n">
         <v>0.8806067790683419</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.408030845621036</v>
+        <v>3.310487717551571</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.871374754193889</v>
+        <v>2.773831626124425</v>
       </c>
       <c r="D1993" t="n">
         <v>-2.537829988381081</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.855886334527709</v>
+        <v>1.758343206458245</v>
       </c>
       <c r="F1993" t="n">
         <v>0.8806067790683419</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.399738821634894</v>
+        <v>3.30219569356543</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.869567949777668</v>
+        <v>2.772024821708204</v>
       </c>
       <c r="D1994" t="n">
         <v>-2.459698807532134</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.885332002451068</v>
+        <v>1.787788874381603</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9547835899520265</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.442438103748885</v>
+        <v>3.34489497567942</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.88712235550446</v>
+        <v>2.789579227434996</v>
       </c>
       <c r="D1995" t="n">
         <v>-2.450806346138851</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.906443392735172</v>
+        <v>1.808900264665708</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9547835899520265</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.459992509475676</v>
+        <v>3.362449381406212</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.878977402909044</v>
+        <v>2.78143427483958</v>
       </c>
       <c r="D1996" t="n">
         <v>-2.619282463108729</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.830907993351805</v>
+        <v>1.733364865282341</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9268357542354457</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.435078855450311</v>
+        <v>3.337535727380847</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.860247100096906</v>
+        <v>2.762703972027441</v>
       </c>
       <c r="D1997" t="n">
         <v>-1.921482934247146</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.0912975020843</v>
+        <v>1.993754374014836</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8564876948650351</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.374139717015927</v>
+        <v>3.276596588946463</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.85091112259381</v>
+        <v>2.753367994524346</v>
       </c>
       <c r="D1998" t="n">
         <v>-1.898761830563993</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.091049966054466</v>
+        <v>1.993506837985001</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8564876948650351</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.364803739512832</v>
+        <v>3.267260611443367</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.009817248444979</v>
+        <v>2.912274120375515</v>
       </c>
       <c r="D1999" t="n">
         <v>-1.897036787273949</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.250646109221652</v>
+        <v>2.153102981152188</v>
       </c>
       <c r="F1999" t="n">
         <v>0.8582127381550788</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.524744891338027</v>
+        <v>3.427201763268562</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.046895070938626</v>
+        <v>2.949351942869161</v>
       </c>
       <c r="D2000" t="n">
         <v>-2.051817794052205</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.225811529003997</v>
+        <v>2.128268400934533</v>
       </c>
       <c r="F2000" t="n">
         <v>0.8248450641006027</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.541802109398988</v>
+        <v>3.444258981329523</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.043570426928171</v>
+        <v>2.946027298858707</v>
       </c>
       <c r="D2001" t="n">
         <v>-2.000382460667545</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.243061018347406</v>
+        <v>2.145517890277941</v>
       </c>
       <c r="F2001" t="n">
         <v>0.8762803974852623</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.569338665419329</v>
+        <v>3.471795537349864</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.053576580572912</v>
+        <v>2.956033452503448</v>
       </c>
       <c r="D2002" t="n">
         <v>-1.973431236341057</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.263847661722743</v>
+        <v>2.166304533653278</v>
       </c>
       <c r="F2002" t="n">
         <v>0.8911607435129815</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.588273026680702</v>
+        <v>3.490729898611237</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.237679712717872</v>
+        <v>3.140136584648408</v>
       </c>
       <c r="D2003" t="n">
         <v>-2.109384244397373</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.393569590645176</v>
+        <v>2.296026462575711</v>
       </c>
       <c r="F2003" t="n">
         <v>0.8911607435129815</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.772376158825661</v>
+        <v>3.674833030756197</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.229796407620865</v>
+        <v>3.132253279551401</v>
       </c>
       <c r="D2004" t="n">
         <v>-2.131792362202245</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.37672303842622</v>
+        <v>2.279179910356756</v>
       </c>
       <c r="F2004" t="n">
         <v>0.8911607435129815</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.764492853728655</v>
+        <v>3.66694972565919</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.231850407170503</v>
+        <v>3.134307279101038</v>
       </c>
       <c r="D2005" t="n">
         <v>-2.279798129681645</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.319574730984097</v>
+        <v>2.222031602914633</v>
       </c>
       <c r="F2005" t="n">
         <v>0.80443373464944</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.714510647960167</v>
+        <v>3.616967519890703</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.28810412489235</v>
+        <v>3.190560996822886</v>
       </c>
       <c r="D2006" t="n">
         <v>-2.289239055570174</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.372052078350533</v>
+        <v>2.274508950281068</v>
       </c>
       <c r="F2006" t="n">
         <v>0.9268608521928314</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.844220636208049</v>
+        <v>3.746677508138585</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.290995219437651</v>
+        <v>3.193452091368187</v>
       </c>
       <c r="D2007" t="n">
         <v>-2.287952292030618</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.375457878311656</v>
+        <v>2.277914750242192</v>
       </c>
       <c r="F2007" t="n">
         <v>0.928147615732388</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.847883788877084</v>
+        <v>3.75034066080762</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.289107032331426</v>
+        <v>3.191563904261962</v>
       </c>
       <c r="D2008" t="n">
         <v>-2.289509346019909</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.372946869609715</v>
+        <v>2.275403741540251</v>
       </c>
       <c r="F2008" t="n">
         <v>0.928147615732388</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.845995601770859</v>
+        <v>3.748452473701395</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.283927261934288</v>
+        <v>3.186384133864824</v>
       </c>
       <c r="D2009" t="n">
         <v>-2.296781231543374</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.364858345003191</v>
+        <v>2.267315216933727</v>
       </c>
       <c r="F2009" t="n">
         <v>0.9208757302089232</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.836452700059643</v>
+        <v>3.738909571990178</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.282361272144441</v>
+        <v>3.184818144074976</v>
       </c>
       <c r="D2010" t="n">
         <v>-2.294940212485123</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.364028762836644</v>
+        <v>2.26648563476718</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9221439568803916</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.835647646272676</v>
+        <v>3.738104518203212</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.295434679010359</v>
+        <v>3.197891550940895</v>
       </c>
       <c r="D2011" t="n">
         <v>-2.301848917984803</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.374338687502691</v>
+        <v>2.276795559433226</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9221439568803916</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.848721053138594</v>
+        <v>3.75117792506913</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.295434679010359</v>
+        <v>3.197891550940895</v>
       </c>
       <c r="D2012" t="n">
         <v>-2.303410560799663</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.373714030376747</v>
+        <v>2.276170902307283</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9221439568803916</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.848721053138594</v>
+        <v>3.75117792506913</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.293958720137361</v>
+        <v>3.196415592067897</v>
       </c>
       <c r="D2013" t="n">
         <v>-2.331311347909136</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.361077756659959</v>
+        <v>2.263534628590495</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8875470327374568</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.826486939779835</v>
+        <v>3.728943811710371</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.29072316411456</v>
+        <v>3.193180036045096</v>
       </c>
       <c r="D2014" t="n">
         <v>-2.33434434542181</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.356629001632089</v>
+        <v>2.259085873562625</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8845140352247829</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.82143158524943</v>
+        <v>3.723888457179966</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.357429123705064</v>
+        <v>3.259885995635599</v>
       </c>
       <c r="D2015" t="n">
         <v>-2.354405666698317</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.41531043271199</v>
+        <v>2.317767304642525</v>
       </c>
       <c r="F2015" t="n">
         <v>0.8644527139482758</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.876100752074029</v>
+        <v>3.778557624004565</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.497740842706911</v>
+        <v>3.400197714637446</v>
       </c>
       <c r="D2016" t="n">
         <v>-2.611126484693141</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.452933824515907</v>
+        <v>2.355390696446443</v>
       </c>
       <c r="F2016" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.951363726589587</v>
+        <v>3.853820598520123</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.566721111852551</v>
+        <v>3.469177983783086</v>
       </c>
       <c r="D2017" t="n">
         <v>-2.765112902469281</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.460319526551091</v>
+        <v>2.362776398481627</v>
       </c>
       <c r="F2017" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.020343995735227</v>
+        <v>3.922800867665763</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.552772313972671</v>
+        <v>3.455229185903207</v>
       </c>
       <c r="D2018" t="n">
         <v>-2.714590998641615</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.466579490202278</v>
+        <v>2.369036362132814</v>
       </c>
       <c r="F2018" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.006395197855348</v>
+        <v>3.908852069785884</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.564642803028085</v>
+        <v>3.467099674958621</v>
       </c>
       <c r="D2019" t="n">
         <v>-2.96706615264934</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.377459917654602</v>
+        <v>2.279916789585138</v>
       </c>
       <c r="F2019" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.018265686910762</v>
+        <v>3.920722558841298</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.565853337547029</v>
+        <v>3.468310209477565</v>
       </c>
       <c r="D2020" t="n">
         <v>-3.236538954571048</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.270881331404863</v>
+        <v>2.173338203335399</v>
       </c>
       <c r="F2020" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.019476221429706</v>
+        <v>3.921933093360241</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.795307907771154</v>
+        <v>3.82238645710082</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.569975079774351</v>
+        <v>3.472431951704886</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.389835814827719</v>
+        <v>-3.39408302630049</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.213684329529515</v>
+        <v>2.114442316870943</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6911839319548028</v>
+        <v>0.6891363346641866</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.984685438947232</v>
+        <v>3.885913752503399</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240711.xlsx
+++ b/tame_output/ON/bt/strategyON_20240711.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-71.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.4%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.7%</t>
+          <t>-66.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-501.0%</t>
+          <t>-490.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-50.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.8%</t>
+          <t>-160.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-125.5%</t>
+          <t>-126.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-155.1%</t>
+          <t>-162.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-57.4%</t>
+          <t>-61.6%</t>
         </is>
       </c>
     </row>
@@ -46792,10 +46792,10 @@
         <v>2.487261445495994</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.47612718431148</v>
+        <v>-3.224132878728355</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.096454147457655</v>
+        <v>1.197251869690905</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3303187745317229</v>
@@ -46815,10 +46815,10 @@
         <v>2.487923793887653</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.469974478258695</v>
+        <v>-3.21798017267557</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.099577578270427</v>
+        <v>1.200375300503677</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3364714805845072</v>
@@ -46838,10 +46838,10 @@
         <v>2.487004270627763</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.486783776409197</v>
+        <v>-3.234789470826072</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.091934335750337</v>
+        <v>1.192732057983587</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3196621824340056</v>
@@ -46861,10 +46861,10 @@
         <v>2.553339824424584</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.424485777633075</v>
+        <v>-3.17249147204995</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.183189089057607</v>
+        <v>1.283986811290857</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3196621824340056</v>
@@ -46884,10 +46884,10 @@
         <v>2.355631826138711</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.222695579967917</v>
+        <v>-2.970701274384792</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.066197169837797</v>
+        <v>1.166994892071047</v>
       </c>
       <c r="F1971" t="n">
         <v>0.51768037460316</v>
@@ -46907,10 +46907,10 @@
         <v>2.425922058460886</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.149317482879181</v>
+        <v>-2.897323177296055</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.165838640995467</v>
+        <v>1.266636363228717</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5910584716918965</v>
@@ -46930,10 +46930,10 @@
         <v>2.44054979457693</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.247058027504155</v>
+        <v>-2.99506372192103</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.141370159261521</v>
+        <v>1.242167881494771</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5751691935589163</v>
@@ -46953,10 +46953,10 @@
         <v>2.439085775401602</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.423395787627084</v>
+        <v>-3.171401482043959</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.069371036037021</v>
+        <v>1.170168758270271</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3988314334359869</v>
@@ -46976,10 +46976,10 @@
         <v>2.43757739344153</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.346973741195157</v>
+        <v>-3.094979435612032</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.09843147264972</v>
+        <v>1.19922919488297</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3988314334359869</v>
@@ -46999,10 +46999,10 @@
         <v>2.437440260876966</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.302600609556589</v>
+        <v>-3.050606303973463</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.116043592740584</v>
+        <v>1.216841314973834</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4432045650745555</v>
@@ -47022,10 +47022,10 @@
         <v>2.431834055015557</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.179766388669421</v>
+        <v>-2.927772083086296</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.159571075234041</v>
+        <v>1.260368797467291</v>
       </c>
       <c r="F1977" t="n">
         <v>0.4432045650745555</v>
@@ -47045,10 +47045,10 @@
         <v>2.438215812043361</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.132110658108366</v>
+        <v>-2.88011635252524</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.185015124486267</v>
+        <v>1.285812846719518</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4908602956356112</v>
@@ -47068,10 +47068,10 @@
         <v>2.443108185418086</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.031592499609611</v>
+        <v>-2.779598194026486</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.230114761260494</v>
+        <v>1.330912483493744</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5913784541343657</v>
@@ -47091,10 +47091,10 @@
         <v>2.429862857893958</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.092259090012</v>
+        <v>-2.840264784428875</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.192602797575411</v>
+        <v>1.293400519808661</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5096801374158321</v>
@@ -47114,10 +47114,10 @@
         <v>2.433960560504587</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.047420688403602</v>
+        <v>-2.795426382820477</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.214635860829398</v>
+        <v>1.315433583062649</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5142235703607015</v>
@@ -47137,10 +47137,10 @@
         <v>2.438121500135665</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.148179324160601</v>
+        <v>-2.896185018577475</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.178493346157677</v>
+        <v>1.279291068390927</v>
       </c>
       <c r="F1982" t="n">
         <v>0.4253980016336961</v>
@@ -47160,10 +47160,10 @@
         <v>2.444001102663502</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.1039764870747</v>
+        <v>-2.851982181491575</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.202054083519874</v>
+        <v>1.302851805753125</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4696008387195966</v>
@@ -47183,10 +47183,10 @@
         <v>2.442411103132749</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.140955514738144</v>
+        <v>-2.888961209155018</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.185672472923745</v>
+        <v>1.286470195156995</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5065747405109271</v>
@@ -47206,10 +47206,10 @@
         <v>2.493658868315789</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.982664097198871</v>
+        <v>-2.730669791615746</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.300236805122493</v>
+        <v>1.401034527355743</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5065747405109271</v>
@@ -47229,10 +47229,10 @@
         <v>2.492099572910042</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.775022093564395</v>
+        <v>-2.523027787981269</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.381734311170537</v>
+        <v>1.482532033403787</v>
       </c>
       <c r="F1986" t="n">
         <v>0.7142167441454033</v>
@@ -47252,10 +47252,10 @@
         <v>2.487047801148312</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.723990000841867</v>
+        <v>-2.471995695258741</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.397095376497818</v>
+        <v>1.497893098731068</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7652488368679312</v>
@@ -47275,10 +47275,10 @@
         <v>2.504235205241017</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.658765819714661</v>
+        <v>-2.406771514131536</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.440372453041405</v>
+        <v>1.541170175274656</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8304730179951368</v>
@@ -47298,10 +47298,10 @@
         <v>2.500196177540297</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.621338799643528</v>
+        <v>-2.369344494060402</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.451304233369139</v>
+        <v>1.55210195560239</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8357245560243185</v>
@@ -47321,10 +47321,10 @@
         <v>2.501452969871538</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.641450455678236</v>
+        <v>-2.38945615009511</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.444516363286496</v>
+        <v>1.545314085519746</v>
       </c>
       <c r="F1990" t="n">
         <v>0.8467519010217377</v>
@@ -47344,10 +47344,10 @@
         <v>2.662010740892748</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.587705641251031</v>
+        <v>-2.335711335667905</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.626572060078589</v>
+        <v>1.727369782311839</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8568152104621997</v>
@@ -47367,10 +47367,10 @@
         <v>2.782123650110566</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.563914072644889</v>
+        <v>-2.311919767061763</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.756201596738863</v>
+        <v>1.856999318972113</v>
       </c>
       <c r="F1992" t="n">
         <v>0.8806067790683419</v>
@@ -47390,10 +47390,10 @@
         <v>2.773831626124425</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.537829988381081</v>
+        <v>-2.285835682797955</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.758343206458245</v>
+        <v>1.859140928691495</v>
       </c>
       <c r="F1993" t="n">
         <v>0.8806067790683419</v>
@@ -47413,10 +47413,10 @@
         <v>2.772024821708204</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.459698807532134</v>
+        <v>-2.207704501949008</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.787788874381603</v>
+        <v>1.888586596614854</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9547835899520265</v>
@@ -47436,10 +47436,10 @@
         <v>2.789579227434996</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.450806346138851</v>
+        <v>-2.198812040555725</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.808900264665708</v>
+        <v>1.909697986898958</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9547835899520265</v>
@@ -47459,10 +47459,10 @@
         <v>2.78143427483958</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.619282463108729</v>
+        <v>-2.367288157525603</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.733364865282341</v>
+        <v>1.834162587515591</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9268357542354457</v>
@@ -47482,10 +47482,10 @@
         <v>2.762703972027441</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.921482934247146</v>
+        <v>-1.66948862866402</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.993754374014836</v>
+        <v>2.094552096248086</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8564876948650351</v>
@@ -47505,10 +47505,10 @@
         <v>2.753367994524346</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.898761830563993</v>
+        <v>-1.646767524980867</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.993506837985001</v>
+        <v>2.094304560218252</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8564876948650351</v>
@@ -47528,10 +47528,10 @@
         <v>2.912274120375515</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.897036787273949</v>
+        <v>-1.645042481690824</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.153102981152188</v>
+        <v>2.253900703385438</v>
       </c>
       <c r="F1999" t="n">
         <v>0.8582127381550788</v>
@@ -47551,10 +47551,10 @@
         <v>2.949351942869161</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.051817794052205</v>
+        <v>-1.799823488469079</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.128268400934533</v>
+        <v>2.229066123167783</v>
       </c>
       <c r="F2000" t="n">
         <v>0.8248450641006027</v>
@@ -47574,10 +47574,10 @@
         <v>2.946027298858707</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.000382460667545</v>
+        <v>-1.748388155084419</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.145517890277941</v>
+        <v>2.246315612511192</v>
       </c>
       <c r="F2001" t="n">
         <v>0.8762803974852623</v>
@@ -47597,10 +47597,10 @@
         <v>2.956033452503448</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.973431236341057</v>
+        <v>-1.721436930757931</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.166304533653278</v>
+        <v>2.267102255886528</v>
       </c>
       <c r="F2002" t="n">
         <v>0.8911607435129815</v>
@@ -47620,10 +47620,10 @@
         <v>3.140136584648408</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.109384244397373</v>
+        <v>-1.857389938814247</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.296026462575711</v>
+        <v>2.396824184808962</v>
       </c>
       <c r="F2003" t="n">
         <v>0.8911607435129815</v>
@@ -47643,10 +47643,10 @@
         <v>3.132253279551401</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.131792362202245</v>
+        <v>-1.879798056619119</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.279179910356756</v>
+        <v>2.379977632590006</v>
       </c>
       <c r="F2004" t="n">
         <v>0.8911607435129815</v>
@@ -47666,10 +47666,10 @@
         <v>3.134307279101038</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.279798129681645</v>
+        <v>-2.027803824098519</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.222031602914633</v>
+        <v>2.322829325147884</v>
       </c>
       <c r="F2005" t="n">
         <v>0.80443373464944</v>
@@ -47689,10 +47689,10 @@
         <v>3.190560996822886</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.289239055570174</v>
+        <v>-2.037244749987049</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.274508950281068</v>
+        <v>2.375306672514319</v>
       </c>
       <c r="F2006" t="n">
         <v>0.9268608521928314</v>
@@ -47712,10 +47712,10 @@
         <v>3.193452091368187</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.287952292030618</v>
+        <v>-2.035957986447492</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.277914750242192</v>
+        <v>2.378712472475442</v>
       </c>
       <c r="F2007" t="n">
         <v>0.928147615732388</v>
@@ -47735,10 +47735,10 @@
         <v>3.191563904261962</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.289509346019909</v>
+        <v>-2.037515040436784</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.275403741540251</v>
+        <v>2.376201463773501</v>
       </c>
       <c r="F2008" t="n">
         <v>0.928147615732388</v>
@@ -47758,10 +47758,10 @@
         <v>3.186384133864824</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.296781231543374</v>
+        <v>-2.044786925960248</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.267315216933727</v>
+        <v>2.368112939166978</v>
       </c>
       <c r="F2009" t="n">
         <v>0.9208757302089232</v>
@@ -47781,10 +47781,10 @@
         <v>3.184818144074976</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.294940212485123</v>
+        <v>-2.042945906901997</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.26648563476718</v>
+        <v>2.36728335700043</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9221439568803916</v>
@@ -47804,10 +47804,10 @@
         <v>3.197891550940895</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.301848917984803</v>
+        <v>-2.049854612401678</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.276795559433226</v>
+        <v>2.377593281666477</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9221439568803916</v>
@@ -47827,10 +47827,10 @@
         <v>3.197891550940895</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.303410560799663</v>
+        <v>-2.051416255216537</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.276170902307283</v>
+        <v>2.376968624540533</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9221439568803916</v>
@@ -47850,10 +47850,10 @@
         <v>3.196415592067897</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.331311347909136</v>
+        <v>-2.07931704232601</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.263534628590495</v>
+        <v>2.364332350823746</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8875470327374568</v>
@@ -47873,10 +47873,10 @@
         <v>3.193180036045096</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.33434434542181</v>
+        <v>-2.082350039838684</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.259085873562625</v>
+        <v>2.359883595795875</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8845140352247829</v>
@@ -47896,10 +47896,10 @@
         <v>3.259885995635599</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.354405666698317</v>
+        <v>-2.102411361115191</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.317767304642525</v>
+        <v>2.418565026875776</v>
       </c>
       <c r="F2015" t="n">
         <v>0.8644527139482758</v>
@@ -47919,10 +47919,10 @@
         <v>3.400197714637446</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.611126484693141</v>
+        <v>-2.359132179110015</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.355390696446443</v>
+        <v>2.456188418679693</v>
       </c>
       <c r="F2016" t="n">
         <v>0.756038139804461</v>
@@ -47942,10 +47942,10 @@
         <v>3.469177983783086</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.765112902469281</v>
+        <v>-2.513118596886156</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.362776398481627</v>
+        <v>2.463574120714877</v>
       </c>
       <c r="F2017" t="n">
         <v>0.756038139804461</v>
@@ -47965,10 +47965,10 @@
         <v>3.455229185903207</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.714590998641615</v>
+        <v>-2.46259669305849</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.369036362132814</v>
+        <v>2.469834084366064</v>
       </c>
       <c r="F2018" t="n">
         <v>0.756038139804461</v>
@@ -47988,10 +47988,10 @@
         <v>3.467099674958621</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.96706615264934</v>
+        <v>-2.715071847066215</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.279916789585138</v>
+        <v>2.380714511818388</v>
       </c>
       <c r="F2019" t="n">
         <v>0.756038139804461</v>
@@ -48011,10 +48011,10 @@
         <v>3.468310209477565</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.236538954571048</v>
+        <v>-2.984544648987923</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.173338203335399</v>
+        <v>2.274135925568649</v>
       </c>
       <c r="F2020" t="n">
         <v>0.756038139804461</v>
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.82238645710082</v>
+        <v>3.844963975148258</v>
       </c>
       <c r="C2021" t="n">
         <v>3.472431951704886</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.39408302630049</v>
+        <v>-3.29036973920174</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.114442316870943</v>
+        <v>2.155927631710443</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6891363346641866</v>
+        <v>0.6195385152230221</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.885913752503399</v>
+        <v>3.8441550608387</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240711.xlsx
+++ b/tame_output/ON/bt/strategyON_20240711.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>79.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.7%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>122.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.1%</t>
+          <t>-66.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-490.6%</t>
+          <t>-485.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-35.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-50.1%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.6%</t>
+          <t>-148.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-126.2%</t>
+          <t>-124.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-162.0%</t>
+          <t>-148.6%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-61.6%</t>
+          <t>-82.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2021"/>
+  <dimension ref="A1:G2022"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.487261445495994</v>
+        <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.224132878728355</v>
+        <v>-3.47612718431148</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.197251869690905</v>
+        <v>1.193997275527119</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3303187745317229</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.685452710215028</v>
+        <v>2.782995838284492</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.487923793887653</v>
+        <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.21798017267557</v>
+        <v>-3.469974478258695</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.200375300503677</v>
+        <v>1.197120706339891</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3364714805845072</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.689806682238357</v>
+        <v>2.787349810307821</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.487004270627763</v>
+        <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.234789470826072</v>
+        <v>-3.486783776409197</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.192732057983587</v>
+        <v>1.189477463819801</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3196621824340056</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.678801580088167</v>
+        <v>2.776344708157631</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.553339824424584</v>
+        <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.17249147204995</v>
+        <v>-3.424485777633075</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.283986811290857</v>
+        <v>1.280732217127071</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3196621824340056</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.745137133884988</v>
+        <v>2.842680261954452</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.355631826138711</v>
+        <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.970701274384792</v>
+        <v>-3.222695579967917</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.166994892071047</v>
+        <v>1.163740297907261</v>
       </c>
       <c r="F1971" t="n">
         <v>0.51768037460316</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.666240050900607</v>
+        <v>2.763783178970071</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.425922058460886</v>
+        <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.897323177296055</v>
+        <v>-3.149317482879181</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.266636363228717</v>
+        <v>1.263381769064931</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5910584716918965</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.780557141476025</v>
+        <v>2.878100269545488</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.44054979457693</v>
+        <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.99506372192103</v>
+        <v>-3.247058027504155</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.242167881494771</v>
+        <v>1.238913287330984</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5751691935589163</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.78565131071228</v>
+        <v>2.883194438781744</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.439085775401602</v>
+        <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.171401482043959</v>
+        <v>-3.423395787627084</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.170168758270271</v>
+        <v>1.166914164106484</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3988314334359869</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.678384635463194</v>
+        <v>2.775927763532658</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.43757739344153</v>
+        <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.094979435612032</v>
+        <v>-3.346973741195157</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.19922919488297</v>
+        <v>1.195974600719184</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3988314334359869</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.676876253503123</v>
+        <v>2.774419381572586</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.437440260876966</v>
+        <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.050606303973463</v>
+        <v>-3.302600609556589</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.216841314973834</v>
+        <v>1.213586720810047</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4432045650745555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.7033629999217</v>
+        <v>2.800906127991164</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.431834055015557</v>
+        <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.927772083086296</v>
+        <v>-3.179766388669421</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.260368797467291</v>
+        <v>1.257114203303505</v>
       </c>
       <c r="F1977" t="n">
         <v>0.4432045650745555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.69775679406029</v>
+        <v>2.795299922129754</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.438215812043361</v>
+        <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.88011635252524</v>
+        <v>-3.132110658108366</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.285812846719518</v>
+        <v>1.282558252555732</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4908602956356112</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.732731989424728</v>
+        <v>2.830275117494192</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.443108185418086</v>
+        <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.779598194026486</v>
+        <v>-3.031592499609611</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.330912483493744</v>
+        <v>1.327657889329958</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5913784541343657</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.797935257898705</v>
+        <v>2.89547838596817</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.429862857893958</v>
+        <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.840264784428875</v>
+        <v>-3.092259090012</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.293400519808661</v>
+        <v>1.290145925644875</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5096801374158321</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.735670940343458</v>
+        <v>2.833214068412922</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.433960560504587</v>
+        <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.795426382820477</v>
+        <v>-3.047420688403602</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.315433583062649</v>
+        <v>1.312178988898863</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5142235703607015</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.742494702721008</v>
+        <v>2.840037830790472</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.438121500135665</v>
+        <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.896185018577475</v>
+        <v>-3.148179324160601</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.279291068390927</v>
+        <v>1.276036474227141</v>
       </c>
       <c r="F1982" t="n">
         <v>0.4253980016336961</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.693360301115883</v>
+        <v>2.790903429185347</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.444001102663502</v>
+        <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.851982181491575</v>
+        <v>-3.1039764870747</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.302851805753125</v>
+        <v>1.299597211589339</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4696008387195966</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.72576160589526</v>
+        <v>2.823304733964724</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.442411103132749</v>
+        <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.888961209155018</v>
+        <v>-3.140955514738144</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.286470195156995</v>
+        <v>1.283215600993209</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5065747405109271</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.746355947439306</v>
+        <v>2.84389907550877</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.493658868315789</v>
+        <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.730669791615746</v>
+        <v>-2.982664097198871</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.401034527355743</v>
+        <v>1.397779933191958</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5065747405109271</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.797603712622346</v>
+        <v>2.89514684069181</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.492099572910042</v>
+        <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.523027787981269</v>
+        <v>-2.775022093564395</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.482532033403787</v>
+        <v>1.479277439240001</v>
       </c>
       <c r="F1986" t="n">
         <v>0.7142167441454033</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.920629619397284</v>
+        <v>3.018172747466749</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.487047801148312</v>
+        <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.471995695258741</v>
+        <v>-2.723990000841867</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.497893098731068</v>
+        <v>1.494638504567282</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7652488368679312</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.946197103269071</v>
+        <v>3.043740231338536</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.504235205241017</v>
+        <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.406771514131536</v>
+        <v>-2.658765819714661</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.541170175274656</v>
+        <v>1.53791558111087</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8304730179951368</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.002519016038099</v>
+        <v>3.100062144107564</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.500196177540297</v>
+        <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.369344494060402</v>
+        <v>-2.621338799643528</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.55210195560239</v>
+        <v>1.548847361438604</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8357245560243185</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.001630911154889</v>
+        <v>3.099174039224353</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.501452969871538</v>
+        <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.38945615009511</v>
+        <v>-2.641450455678236</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.545314085519746</v>
+        <v>1.54205949135596</v>
       </c>
       <c r="F1990" t="n">
         <v>0.8467519010217377</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.009504110484581</v>
+        <v>3.107047238554045</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.662010740892748</v>
+        <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.335711335667905</v>
+        <v>-2.587705641251031</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.727369782311839</v>
+        <v>1.724115188148053</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8568152104621997</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.176099867170068</v>
+        <v>3.273642995239533</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.782123650110566</v>
+        <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.311919767061763</v>
+        <v>-2.563914072644889</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.856999318972113</v>
+        <v>1.853744724808327</v>
       </c>
       <c r="F1992" t="n">
         <v>0.8806067790683419</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.310487717551571</v>
+        <v>3.408030845621036</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.773831626124425</v>
+        <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.285835682797955</v>
+        <v>-2.537829988381081</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.859140928691495</v>
+        <v>1.855886334527709</v>
       </c>
       <c r="F1993" t="n">
         <v>0.8806067790683419</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.30219569356543</v>
+        <v>3.399738821634894</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.772024821708204</v>
+        <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.207704501949008</v>
+        <v>-2.459698807532134</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.888586596614854</v>
+        <v>1.885332002451068</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9547835899520265</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.34489497567942</v>
+        <v>3.442438103748885</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.789579227434996</v>
+        <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.198812040555725</v>
+        <v>-2.450806346138851</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.909697986898958</v>
+        <v>1.906443392735172</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9547835899520265</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.362449381406212</v>
+        <v>3.459992509475676</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.78143427483958</v>
+        <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.367288157525603</v>
+        <v>-2.619282463108729</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.834162587515591</v>
+        <v>1.830907993351805</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9268357542354457</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.337535727380847</v>
+        <v>3.435078855450311</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.762703972027441</v>
+        <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.66948862866402</v>
+        <v>-1.921482934247146</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.094552096248086</v>
+        <v>2.0912975020843</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8564876948650351</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.276596588946463</v>
+        <v>3.374139717015927</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.753367994524346</v>
+        <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.646767524980867</v>
+        <v>-1.898761830563993</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.094304560218252</v>
+        <v>2.091049966054466</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8564876948650351</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.267260611443367</v>
+        <v>3.364803739512832</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.912274120375515</v>
+        <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.645042481690824</v>
+        <v>-1.897036787273949</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.253900703385438</v>
+        <v>2.250646109221652</v>
       </c>
       <c r="F1999" t="n">
         <v>0.8582127381550788</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.427201763268562</v>
+        <v>3.524744891338027</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.949351942869161</v>
+        <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.799823488469079</v>
+        <v>-2.051817794052205</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.229066123167783</v>
+        <v>2.225811529003997</v>
       </c>
       <c r="F2000" t="n">
         <v>0.8248450641006027</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.444258981329523</v>
+        <v>3.541802109398988</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.946027298858707</v>
+        <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.748388155084419</v>
+        <v>-2.000382460667545</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.246315612511192</v>
+        <v>2.243061018347406</v>
       </c>
       <c r="F2001" t="n">
         <v>0.8762803974852623</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.471795537349864</v>
+        <v>3.569338665419329</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.956033452503448</v>
+        <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.721436930757931</v>
+        <v>-1.973431236341057</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.267102255886528</v>
+        <v>2.263847661722743</v>
       </c>
       <c r="F2002" t="n">
         <v>0.8911607435129815</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.490729898611237</v>
+        <v>3.588273026680702</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.140136584648408</v>
+        <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.857389938814247</v>
+        <v>-2.109384244397373</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.396824184808962</v>
+        <v>2.393569590645176</v>
       </c>
       <c r="F2003" t="n">
         <v>0.8911607435129815</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.674833030756197</v>
+        <v>3.772376158825661</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.132253279551401</v>
+        <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.879798056619119</v>
+        <v>-2.131792362202245</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.379977632590006</v>
+        <v>2.37672303842622</v>
       </c>
       <c r="F2004" t="n">
         <v>0.8911607435129815</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.66694972565919</v>
+        <v>3.764492853728655</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.134307279101038</v>
+        <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.027803824098519</v>
+        <v>-2.279798129681645</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.322829325147884</v>
+        <v>2.319574730984097</v>
       </c>
       <c r="F2005" t="n">
         <v>0.80443373464944</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.616967519890703</v>
+        <v>3.714510647960167</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.190560996822886</v>
+        <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.037244749987049</v>
+        <v>-2.289239055570174</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.375306672514319</v>
+        <v>2.372052078350533</v>
       </c>
       <c r="F2006" t="n">
         <v>0.9268608521928314</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.746677508138585</v>
+        <v>3.844220636208049</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.193452091368187</v>
+        <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.035957986447492</v>
+        <v>-2.287952292030618</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.378712472475442</v>
+        <v>2.375457878311656</v>
       </c>
       <c r="F2007" t="n">
         <v>0.928147615732388</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.75034066080762</v>
+        <v>3.847883788877084</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.191563904261962</v>
+        <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.037515040436784</v>
+        <v>-2.289509346019909</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.376201463773501</v>
+        <v>2.372946869609715</v>
       </c>
       <c r="F2008" t="n">
         <v>0.928147615732388</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.748452473701395</v>
+        <v>3.845995601770859</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.186384133864824</v>
+        <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.044786925960248</v>
+        <v>-2.296781231543374</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.368112939166978</v>
+        <v>2.364858345003191</v>
       </c>
       <c r="F2009" t="n">
         <v>0.9208757302089232</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.738909571990178</v>
+        <v>3.836452700059643</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.184818144074976</v>
+        <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.042945906901997</v>
+        <v>-2.294940212485123</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.36728335700043</v>
+        <v>2.364028762836644</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9221439568803916</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.738104518203212</v>
+        <v>3.835647646272676</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.197891550940895</v>
+        <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.049854612401678</v>
+        <v>-2.301848917984803</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.377593281666477</v>
+        <v>2.374338687502691</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9221439568803916</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.75117792506913</v>
+        <v>3.848721053138594</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.197891550940895</v>
+        <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.051416255216537</v>
+        <v>-2.303410560799663</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.376968624540533</v>
+        <v>2.373714030376747</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9221439568803916</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.75117792506913</v>
+        <v>3.848721053138594</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.196415592067897</v>
+        <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.07931704232601</v>
+        <v>-2.331311347909136</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.364332350823746</v>
+        <v>2.361077756659959</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8875470327374568</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.728943811710371</v>
+        <v>3.826486939779835</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.193180036045096</v>
+        <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.082350039838684</v>
+        <v>-2.33434434542181</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.359883595795875</v>
+        <v>2.356629001632089</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8845140352247829</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.723888457179966</v>
+        <v>3.82143158524943</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.259885995635599</v>
+        <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.102411361115191</v>
+        <v>-2.354405666698317</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.418565026875776</v>
+        <v>2.41531043271199</v>
       </c>
       <c r="F2015" t="n">
         <v>0.8644527139482758</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.778557624004565</v>
+        <v>3.876100752074029</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.400197714637446</v>
+        <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.359132179110015</v>
+        <v>-2.611126484693141</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.456188418679693</v>
+        <v>2.452933824515907</v>
       </c>
       <c r="F2016" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.853820598520123</v>
+        <v>3.951363726589587</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.469177983783086</v>
+        <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.513118596886156</v>
+        <v>-2.765112902469281</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.463574120714877</v>
+        <v>2.460319526551091</v>
       </c>
       <c r="F2017" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.922800867665763</v>
+        <v>4.020343995735227</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.455229185903207</v>
+        <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.46259669305849</v>
+        <v>-2.714590998641615</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.469834084366064</v>
+        <v>2.466579490202278</v>
       </c>
       <c r="F2018" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.908852069785884</v>
+        <v>4.006395197855348</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.467099674958621</v>
+        <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.715071847066215</v>
+        <v>-2.96706615264934</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.380714511818388</v>
+        <v>2.377459917654602</v>
       </c>
       <c r="F2019" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.920722558841298</v>
+        <v>4.018265686910762</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.468310209477565</v>
+        <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.984544648987923</v>
+        <v>-3.236538954571048</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.274135925568649</v>
+        <v>2.270881331404863</v>
       </c>
       <c r="F2020" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.921933093360241</v>
+        <v>4.019476221429706</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,45 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.844963975148258</v>
+        <v>3.663523617637087</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.472431951704886</v>
+        <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.29036973920174</v>
+        <v>-3.242026556684406</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.155927631710443</v>
+        <v>2.272808032786841</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6195385152230221</v>
+        <v>0.7540231541900209</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.8441550608387</v>
+        <v>4.022388972288363</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" s="2" t="n">
+        <v>45484</v>
+      </c>
+      <c r="B2022" t="n">
+        <v>3.796708894179611</v>
+      </c>
+      <c r="C2022" t="n">
+        <v>3.643513770761547</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>-3.242026556684406</v>
+      </c>
+      <c r="E2022" t="n">
+        <v>2.272808032786841</v>
+      </c>
+      <c r="F2022" t="n">
+        <v>0.7540231541900209</v>
+      </c>
+      <c r="G2022" t="n">
+        <v>3.636577567747915</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240711.xlsx
+++ b/tame_output/ON/bt/strategyON_20240711.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,47 +834,47 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>64.0%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>30.3%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>66.2%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>76.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.0%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.0%</t>
+          <t>-65.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-485.8%</t>
+          <t>-476.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-148.9%</t>
+          <t>-155.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-124.9%</t>
+          <t>-125.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-148.6%</t>
+          <t>-155.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-82.4%</t>
+          <t>-58.7%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.584804573565458</v>
+        <v>2.487261445495994</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.47612718431148</v>
+        <v>-3.231014338286674</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.193997275527119</v>
+        <v>1.194499285867578</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3303187745317229</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.782995838284492</v>
+        <v>2.685452710215028</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.585466921957117</v>
+        <v>2.487923793887653</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.469974478258695</v>
+        <v>-3.224861632233889</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.197120706339891</v>
+        <v>1.19762271668035</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3364714805845072</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.787349810307821</v>
+        <v>2.689806682238357</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.584547398697227</v>
+        <v>2.487004270627763</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.486783776409197</v>
+        <v>-3.241670930384391</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.189477463819801</v>
+        <v>1.189979474160259</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3196621824340056</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.776344708157631</v>
+        <v>2.678801580088167</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.650882952494048</v>
+        <v>2.553339824424584</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.424485777633075</v>
+        <v>-3.179372931608269</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.280732217127071</v>
+        <v>1.281234227467529</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3196621824340056</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.842680261954452</v>
+        <v>2.745137133884988</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.453174954208175</v>
+        <v>2.355631826138711</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.222695579967917</v>
+        <v>-2.977582733943111</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.163740297907261</v>
+        <v>1.164242308247719</v>
       </c>
       <c r="F1971" t="n">
         <v>0.51768037460316</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.763783178970071</v>
+        <v>2.666240050900607</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.52346518653035</v>
+        <v>2.425922058460886</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.149317482879181</v>
+        <v>-2.904204636854375</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.263381769064931</v>
+        <v>1.263883779405389</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5910584716918965</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.878100269545488</v>
+        <v>2.780557141476025</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.538092922646394</v>
+        <v>2.44054979457693</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.247058027504155</v>
+        <v>-3.001945181479349</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.238913287330984</v>
+        <v>1.239415297671443</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5751691935589163</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.883194438781744</v>
+        <v>2.78565131071228</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.536628903471065</v>
+        <v>2.439085775401602</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.423395787627084</v>
+        <v>-3.178282941602278</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.166914164106484</v>
+        <v>1.167416174446943</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3988314334359869</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.775927763532658</v>
+        <v>2.678384635463194</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.535120521510994</v>
+        <v>2.43757739344153</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.346973741195157</v>
+        <v>-3.101860895170351</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.195974600719184</v>
+        <v>1.196476611059642</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3988314334359869</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.774419381572586</v>
+        <v>2.676876253503123</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.53498338894643</v>
+        <v>2.437440260876966</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.302600609556589</v>
+        <v>-3.057487763531783</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.213586720810047</v>
+        <v>1.214088731150506</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4432045650745555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.800906127991164</v>
+        <v>2.7033629999217</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.529377183085021</v>
+        <v>2.431834055015557</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.179766388669421</v>
+        <v>-2.934653542644615</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.257114203303505</v>
+        <v>1.257616213643963</v>
       </c>
       <c r="F1977" t="n">
         <v>0.4432045650745555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.795299922129754</v>
+        <v>2.69775679406029</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.535758940112825</v>
+        <v>2.438215812043361</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.132110658108366</v>
+        <v>-2.88699781208356</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.282558252555732</v>
+        <v>1.28306026289619</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4908602956356112</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.830275117494192</v>
+        <v>2.732731989424728</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.54065131348755</v>
+        <v>2.443108185418086</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.031592499609611</v>
+        <v>-2.786479653584805</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.327657889329958</v>
+        <v>1.328159899670417</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5913784541343657</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.89547838596817</v>
+        <v>2.797935257898705</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.527405985963422</v>
+        <v>2.429862857893958</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.092259090012</v>
+        <v>-2.847146243987194</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.290145925644875</v>
+        <v>1.290647935985333</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5096801374158321</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.833214068412922</v>
+        <v>2.735670940343458</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.531503688574051</v>
+        <v>2.433960560504587</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.047420688403602</v>
+        <v>-2.802307842378796</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.312178988898863</v>
+        <v>1.312680999239321</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5142235703607015</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.840037830790472</v>
+        <v>2.742494702721008</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.535664628205129</v>
+        <v>2.438121500135665</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.148179324160601</v>
+        <v>-2.903066478135794</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.276036474227141</v>
+        <v>1.2765384845676</v>
       </c>
       <c r="F1982" t="n">
         <v>0.4253980016336961</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.790903429185347</v>
+        <v>2.693360301115883</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.541544230732966</v>
+        <v>2.444001102663502</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.1039764870747</v>
+        <v>-2.858863641049894</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.299597211589339</v>
+        <v>1.300099221929797</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4696008387195966</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.823304733964724</v>
+        <v>2.72576160589526</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.539954231202214</v>
+        <v>2.442411103132749</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.140955514738144</v>
+        <v>-2.895842668713337</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.283215600993209</v>
+        <v>1.283717611333667</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5065747405109271</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.84389907550877</v>
+        <v>2.746355947439306</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.591201996385253</v>
+        <v>2.493658868315789</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.982664097198871</v>
+        <v>-2.737551251174065</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.397779933191958</v>
+        <v>1.398281943532416</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5065747405109271</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.89514684069181</v>
+        <v>2.797603712622346</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.589642700979506</v>
+        <v>2.492099572910042</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.775022093564395</v>
+        <v>-2.529909247539589</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.479277439240001</v>
+        <v>1.479779449580459</v>
       </c>
       <c r="F1986" t="n">
         <v>0.7142167441454033</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.018172747466749</v>
+        <v>2.920629619397284</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.584590929217776</v>
+        <v>2.487047801148312</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.723990000841867</v>
+        <v>-2.478877154817061</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.494638504567282</v>
+        <v>1.495140514907741</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7652488368679312</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.043740231338536</v>
+        <v>2.946197103269071</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.601778333310481</v>
+        <v>2.504235205241017</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.658765819714661</v>
+        <v>-2.413652973689855</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.53791558111087</v>
+        <v>1.538417591451328</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8304730179951368</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.100062144107564</v>
+        <v>3.002519016038099</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.597739305609762</v>
+        <v>2.500196177540297</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.621338799643528</v>
+        <v>-2.376225953618721</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.548847361438604</v>
+        <v>1.549349371779062</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8357245560243185</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.099174039224353</v>
+        <v>3.001630911154889</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.598996097941002</v>
+        <v>2.501452969871538</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.641450455678236</v>
+        <v>-2.396337609653429</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.54205949135596</v>
+        <v>1.542561501696419</v>
       </c>
       <c r="F1990" t="n">
         <v>0.8467519010217377</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.107047238554045</v>
+        <v>3.009504110484581</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.759553868962213</v>
+        <v>2.662010740892748</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.587705641251031</v>
+        <v>-2.342592795226225</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.724115188148053</v>
+        <v>1.724617198488511</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8568152104621997</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.273642995239533</v>
+        <v>3.176099867170068</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.87966677818003</v>
+        <v>2.782123650110566</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.563914072644889</v>
+        <v>-2.318801226620082</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.853744724808327</v>
+        <v>1.854246735148786</v>
       </c>
       <c r="F1992" t="n">
         <v>0.8806067790683419</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.408030845621036</v>
+        <v>3.310487717551571</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.871374754193889</v>
+        <v>2.773831626124425</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.537829988381081</v>
+        <v>-2.292717142356274</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.855886334527709</v>
+        <v>1.856388344868168</v>
       </c>
       <c r="F1993" t="n">
         <v>0.8806067790683419</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.399738821634894</v>
+        <v>3.30219569356543</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.869567949777668</v>
+        <v>2.772024821708204</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.459698807532134</v>
+        <v>-2.214585961507328</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.885332002451068</v>
+        <v>1.885834012791526</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9547835899520265</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.442438103748885</v>
+        <v>3.34489497567942</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.88712235550446</v>
+        <v>2.789579227434996</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.450806346138851</v>
+        <v>-2.205693500114045</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.906443392735172</v>
+        <v>1.906945403075631</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9547835899520265</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.459992509475676</v>
+        <v>3.362449381406212</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.878977402909044</v>
+        <v>2.78143427483958</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.619282463108729</v>
+        <v>-2.374169617083922</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.830907993351805</v>
+        <v>1.831410003692263</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9268357542354457</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.435078855450311</v>
+        <v>3.337535727380847</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.860247100096906</v>
+        <v>2.762703972027441</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.921482934247146</v>
+        <v>-1.676370088222339</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.0912975020843</v>
+        <v>2.091799512424759</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8564876948650351</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.374139717015927</v>
+        <v>3.276596588946463</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.85091112259381</v>
+        <v>2.753367994524346</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.898761830563993</v>
+        <v>-1.653648984539187</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.091049966054466</v>
+        <v>2.091551976394924</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8564876948650351</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.364803739512832</v>
+        <v>3.267260611443367</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.009817248444979</v>
+        <v>2.912274120375515</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.897036787273949</v>
+        <v>-1.651923941249143</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.250646109221652</v>
+        <v>2.251148119562111</v>
       </c>
       <c r="F1999" t="n">
         <v>0.8582127381550788</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.524744891338027</v>
+        <v>3.427201763268562</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.046895070938626</v>
+        <v>2.949351942869161</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.051817794052205</v>
+        <v>-1.806704948027398</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.225811529003997</v>
+        <v>2.226313539344455</v>
       </c>
       <c r="F2000" t="n">
         <v>0.8248450641006027</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.541802109398988</v>
+        <v>3.444258981329523</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.043570426928171</v>
+        <v>2.946027298858707</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.000382460667545</v>
+        <v>-1.755269614642739</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.243061018347406</v>
+        <v>2.243563028687864</v>
       </c>
       <c r="F2001" t="n">
         <v>0.8762803974852623</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.569338665419329</v>
+        <v>3.471795537349864</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.053576580572912</v>
+        <v>2.956033452503448</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.973431236341057</v>
+        <v>-1.728318390316251</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.263847661722743</v>
+        <v>2.264349672063201</v>
       </c>
       <c r="F2002" t="n">
         <v>0.8911607435129815</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.588273026680702</v>
+        <v>3.490729898611237</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.237679712717872</v>
+        <v>3.140136584648408</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.109384244397373</v>
+        <v>-1.864271398372567</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.393569590645176</v>
+        <v>2.394071600985634</v>
       </c>
       <c r="F2003" t="n">
         <v>0.8911607435129815</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.772376158825661</v>
+        <v>3.674833030756197</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.229796407620865</v>
+        <v>3.132253279551401</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.131792362202245</v>
+        <v>-1.886679516177439</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.37672303842622</v>
+        <v>2.377225048766678</v>
       </c>
       <c r="F2004" t="n">
         <v>0.8911607435129815</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.764492853728655</v>
+        <v>3.66694972565919</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.231850407170503</v>
+        <v>3.134307279101038</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.279798129681645</v>
+        <v>-2.034685283656838</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.319574730984097</v>
+        <v>2.320076741324556</v>
       </c>
       <c r="F2005" t="n">
         <v>0.80443373464944</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.714510647960167</v>
+        <v>3.616967519890703</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.28810412489235</v>
+        <v>3.190560996822886</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.289239055570174</v>
+        <v>-2.044126209545368</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.372052078350533</v>
+        <v>2.372554088690991</v>
       </c>
       <c r="F2006" t="n">
         <v>0.9268608521928314</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.844220636208049</v>
+        <v>3.746677508138585</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.290995219437651</v>
+        <v>3.193452091368187</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.287952292030618</v>
+        <v>-2.042839446005812</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.375457878311656</v>
+        <v>2.375959888652114</v>
       </c>
       <c r="F2007" t="n">
         <v>0.928147615732388</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.847883788877084</v>
+        <v>3.75034066080762</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.289107032331426</v>
+        <v>3.191563904261962</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.289509346019909</v>
+        <v>-2.044396499995103</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.372946869609715</v>
+        <v>2.373448879950173</v>
       </c>
       <c r="F2008" t="n">
         <v>0.928147615732388</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.845995601770859</v>
+        <v>3.748452473701395</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.283927261934288</v>
+        <v>3.186384133864824</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.296781231543374</v>
+        <v>-2.051668385518568</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.364858345003191</v>
+        <v>2.36536035534365</v>
       </c>
       <c r="F2009" t="n">
         <v>0.9208757302089232</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.836452700059643</v>
+        <v>3.738909571990178</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.282361272144441</v>
+        <v>3.184818144074976</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.294940212485123</v>
+        <v>-2.049827366460316</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.364028762836644</v>
+        <v>2.364530773177103</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9221439568803916</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.835647646272676</v>
+        <v>3.738104518203212</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.295434679010359</v>
+        <v>3.197891550940895</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.301848917984803</v>
+        <v>-2.056736071959997</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.374338687502691</v>
+        <v>2.374840697843149</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9221439568803916</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.848721053138594</v>
+        <v>3.75117792506913</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.295434679010359</v>
+        <v>3.197891550940895</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.303410560799663</v>
+        <v>-2.058297714774857</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.373714030376747</v>
+        <v>2.374216040717205</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9221439568803916</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.848721053138594</v>
+        <v>3.75117792506913</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.293958720137361</v>
+        <v>3.196415592067897</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.331311347909136</v>
+        <v>-2.08619850188433</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.361077756659959</v>
+        <v>2.361579767000418</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8875470327374568</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.826486939779835</v>
+        <v>3.728943811710371</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.29072316411456</v>
+        <v>3.193180036045096</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.33434434542181</v>
+        <v>-2.089231499397004</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.356629001632089</v>
+        <v>2.357131011972547</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8845140352247829</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.82143158524943</v>
+        <v>3.723888457179966</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.357429123705064</v>
+        <v>3.259885995635599</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.354405666698317</v>
+        <v>-2.10929282067351</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.41531043271199</v>
+        <v>2.415812443052448</v>
       </c>
       <c r="F2015" t="n">
         <v>0.8644527139482758</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.876100752074029</v>
+        <v>3.778557624004565</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.497740842706911</v>
+        <v>3.400197714637446</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.611126484693141</v>
+        <v>-2.366013638668334</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.452933824515907</v>
+        <v>2.453435834856366</v>
       </c>
       <c r="F2016" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.951363726589587</v>
+        <v>3.853820598520123</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.566721111852551</v>
+        <v>3.469177983783086</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.765112902469281</v>
+        <v>-2.520000056444475</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.460319526551091</v>
+        <v>2.460821536891549</v>
       </c>
       <c r="F2017" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.020343995735227</v>
+        <v>3.922800867665763</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.552772313972671</v>
+        <v>3.455229185903207</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.714590998641615</v>
+        <v>-2.469478152616809</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.466579490202278</v>
+        <v>2.467081500542736</v>
       </c>
       <c r="F2018" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.006395197855348</v>
+        <v>3.908852069785884</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.564642803028085</v>
+        <v>3.467099674958621</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.96706615264934</v>
+        <v>-2.721953306624534</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.377459917654602</v>
+        <v>2.37796192799506</v>
       </c>
       <c r="F2019" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.018265686910762</v>
+        <v>3.920722558841298</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.565853337547029</v>
+        <v>3.468310209477565</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.236538954571048</v>
+        <v>-2.991426108546242</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.270881331404863</v>
+        <v>2.271383341745321</v>
       </c>
       <c r="F2020" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.019476221429706</v>
+        <v>3.921933093360241</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663523617637087</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.569975079774351</v>
+        <v>3.472431951704886</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.242026556684406</v>
+        <v>-3.148970180275683</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.272808032786841</v>
+        <v>2.212487455280866</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7540231541900209</v>
+        <v>0.6891363346641866</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.022388972288363</v>
+        <v>3.885913752503399</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.796708894179611</v>
+        <v>3.846892850544258</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.643513770761547</v>
+        <v>3.879810186185204</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.242026556684406</v>
+        <v>-3.148970180275683</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.272808032786841</v>
+        <v>2.212487455280866</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7540231541900209</v>
+        <v>0.6891363346641866</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.636577567747915</v>
+        <v>3.872873983171571</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240711.xlsx
+++ b/tame_output/ON/bt/strategyON_20240711.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,47 +834,47 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>64.7%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>30.4%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>66.2%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>122.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.6%</t>
+          <t>-66.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.5%</t>
+          <t>457.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-476.5%</t>
+          <t>-488.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.0%</t>
+          <t>-150.1%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-125.4%</t>
+          <t>-125.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-58.7%</t>
+          <t>-80.5%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.467083454248663</v>
+        <v>-4.344732585605771</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.177122189563462</v>
+        <v>1.226062537020619</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.09751751343782861</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.414085131967275</v>
+        <v>-4.291734263324384</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.199000102393357</v>
+        <v>1.247940449850514</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.04218125443588977</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.305280246487548</v>
+        <v>-4.182929377844657</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.239520127805242</v>
+        <v>1.288460475262398</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.04218125443588977</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.085259448450538</v>
+        <v>-3.962908579807646</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.32910748403066</v>
+        <v>1.378047831487817</v>
       </c>
       <c r="F1929" t="n">
         <v>0.09903859063209047</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.95239175938726</v>
+        <v>-3.830040890744367</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.398148742457795</v>
+        <v>1.447089089914952</v>
       </c>
       <c r="F1930" t="n">
         <v>0.09903859063209047</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.832218676022761</v>
+        <v>-3.709867807379869</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.447363820243896</v>
+        <v>1.496304167701053</v>
       </c>
       <c r="F1931" t="n">
         <v>0.2192116739965894</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.687546530923023</v>
+        <v>-3.565195662280131</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.515320780845231</v>
+        <v>1.564261128302388</v>
       </c>
       <c r="F1932" t="n">
         <v>0.3638838190963268</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.747421358280715</v>
+        <v>-3.625070489637824</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.47740834130358</v>
+        <v>1.526348688760736</v>
       </c>
       <c r="F1933" t="n">
         <v>0.3040089917386347</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.627601127369878</v>
+        <v>-3.505250258726986</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.540625602902123</v>
+        <v>1.58956595035928</v>
       </c>
       <c r="F1934" t="n">
         <v>0.3040089917386347</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.630070833831684</v>
+        <v>-3.507719965188792</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.447281919639843</v>
+        <v>1.496222267096999</v>
       </c>
       <c r="F1935" t="n">
         <v>0.3015392852768286</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.698441020155694</v>
+        <v>-3.576090151512802</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.33919570659554</v>
+        <v>1.388136054052697</v>
       </c>
       <c r="F1936" t="n">
         <v>0.3108149843130435</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.712229073002741</v>
+        <v>-3.589878204359849</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.324117194088613</v>
+        <v>1.373057541545769</v>
       </c>
       <c r="F1937" t="n">
         <v>0.3108149843130435</v>
@@ -46125,10 +46125,10 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.743222232331446</v>
+        <v>-3.620871363688554</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.136429495397517</v>
+        <v>1.185369842854674</v>
       </c>
       <c r="F1938" t="n">
         <v>0.3108149843130435</v>
@@ -46148,10 +46148,10 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.567747972538977</v>
+        <v>-3.445397103896085</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.211186431306293</v>
+        <v>1.260126778763449</v>
       </c>
       <c r="F1939" t="n">
         <v>0.3108149843130435</v>
@@ -46171,10 +46171,10 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.678684225180225</v>
+        <v>-3.556333356537333</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.142553959011</v>
+        <v>1.191494306468157</v>
       </c>
       <c r="F1940" t="n">
         <v>0.3108149843130435</v>
@@ -46194,10 +46194,10 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.645020679707943</v>
+        <v>-3.522669811065052</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.159150762419819</v>
+        <v>1.208091109876975</v>
       </c>
       <c r="F1941" t="n">
         <v>0.3444785297853253</v>
@@ -46217,10 +46217,10 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.58516806050422</v>
+        <v>-3.462817191861328</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.19326419653344</v>
+        <v>1.242204543990597</v>
       </c>
       <c r="F1942" t="n">
         <v>0.3444785297853253</v>
@@ -46240,10 +46240,10 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.498924597477843</v>
+        <v>-3.376573728834951</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.222707852317852</v>
+        <v>1.271648199775008</v>
       </c>
       <c r="F1943" t="n">
         <v>0.3444785297853253</v>
@@ -46263,10 +46263,10 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.544231416876823</v>
+        <v>-3.421880548233931</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.196360900002785</v>
+        <v>1.245301247459942</v>
       </c>
       <c r="F1944" t="n">
         <v>0.3036683667760945</v>
@@ -46286,10 +46286,10 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.573264521579124</v>
+        <v>-3.450913652936233</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.185299531154966</v>
+        <v>1.234239878612123</v>
       </c>
       <c r="F1945" t="n">
         <v>0.3036683667760945</v>
@@ -46309,10 +46309,10 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.480454040128265</v>
+        <v>-3.358103171485373</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.151696415626675</v>
+        <v>1.200636763083832</v>
       </c>
       <c r="F1946" t="n">
         <v>0.3964788482269539</v>
@@ -46332,10 +46332,10 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.524843509457693</v>
+        <v>-3.402492640814801</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.135814103819505</v>
+        <v>1.184754451276662</v>
       </c>
       <c r="F1947" t="n">
         <v>0.3520893788975262</v>
@@ -46355,10 +46355,10 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.412172291221442</v>
+        <v>-3.289821422578551</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.175958299625728</v>
+        <v>1.224898647082885</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4647605971337764</v>
@@ -46378,10 +46378,10 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.29979529003877</v>
+        <v>-3.177444421395878</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.226400395929464</v>
+        <v>1.275340743386621</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4647605971337764</v>
@@ -46401,10 +46401,10 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.327575687940123</v>
+        <v>-3.205224819297231</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.226785438537462</v>
+        <v>1.275725785994619</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4369801992324234</v>
@@ -46424,10 +46424,10 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.410576968965402</v>
+        <v>-3.28822610032251</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.031940646128004</v>
+        <v>1.080880993585161</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4184093147052496</v>
@@ -46447,10 +46447,10 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.519191047408733</v>
+        <v>-3.396840178765841</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.108644675469877</v>
+        <v>1.157585022927034</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4184093147052496</v>
@@ -46470,10 +46470,10 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.48378200916059</v>
+        <v>-3.361431140517698</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.137321316871457</v>
+        <v>1.186261664328614</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4184093147052496</v>
@@ -46493,10 +46493,10 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.445398346602439</v>
+        <v>-3.323047477959547</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.150094223237087</v>
+        <v>1.199034570694243</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4567929772634008</v>
@@ -46516,10 +46516,10 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.268282016567273</v>
+        <v>-3.145931147924381</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.217669784096455</v>
+        <v>1.266610131553612</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4567929772634008</v>
@@ -46539,10 +46539,10 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.313374261400819</v>
+        <v>-3.191023392757927</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.20031627792495</v>
+        <v>1.249256625382107</v>
       </c>
       <c r="F1956" t="n">
         <v>0.394896934094011</v>
@@ -46562,10 +46562,10 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.133998840162051</v>
+        <v>-3.011647971519159</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.265853421726872</v>
+        <v>1.314793769184028</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5516736922647296</v>
@@ -46585,10 +46585,10 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.179013053682657</v>
+        <v>-3.056662185039766</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.228655191650219</v>
+        <v>1.277595539107375</v>
       </c>
       <c r="F1958" t="n">
         <v>0.521324796950125</v>
@@ -46608,10 +46608,10 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.446017563955093</v>
+        <v>-3.323666695312201</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.12754494988019</v>
+        <v>1.176485297337347</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3269617589071764</v>
@@ -46631,10 +46631,10 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.547215345392265</v>
+        <v>-3.424864476749374</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.086269759201823</v>
+        <v>1.135210106658979</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2585529453618572</v>
@@ -46654,10 +46654,10 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.540704378777953</v>
+        <v>-3.418353510135061</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.086474107401864</v>
+        <v>1.135414454859021</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2585529453618572</v>
@@ -46677,10 +46677,10 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.521666251070656</v>
+        <v>-3.399315382427764</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.090614077693028</v>
+        <v>1.139554425150185</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2003693340306627</v>
@@ -46700,10 +46700,10 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.552792882221274</v>
+        <v>-3.430442013578382</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.255745294171462</v>
+        <v>1.304685641628618</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2003693340306627</v>
@@ -46723,10 +46723,10 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.566659643555191</v>
+        <v>-3.444308774912299</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.251031918624028</v>
+        <v>1.299972266081185</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1625114172968398</v>
@@ -46746,10 +46746,10 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.521855472015261</v>
+        <v>-3.399504603372369</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.274962117636926</v>
+        <v>1.323902465094083</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1625114172968398</v>
@@ -46769,10 +46769,10 @@
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.374112501780259</v>
+        <v>-3.251761633137367</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.232009527008127</v>
+        <v>1.280949874465283</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3303187745317229</v>
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.487261445495994</v>
+        <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.231014338286674</v>
+        <v>-3.353776315668588</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.194499285867578</v>
+        <v>1.242937622984276</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3303187745317229</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.685452710215028</v>
+        <v>2.782995838284492</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.487923793887653</v>
+        <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.224861632233889</v>
+        <v>-3.347623609615804</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.19762271668035</v>
+        <v>1.246061053797048</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3364714805845072</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.689806682238357</v>
+        <v>2.787349810307821</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.487004270627763</v>
+        <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.241670930384391</v>
+        <v>-3.364432907766305</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.189979474160259</v>
+        <v>1.238417811276958</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3196621824340056</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.678801580088167</v>
+        <v>2.776344708157631</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.553339824424584</v>
+        <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.179372931608269</v>
+        <v>-3.302134908990183</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.281234227467529</v>
+        <v>1.329672564584227</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3196621824340056</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.745137133884988</v>
+        <v>2.842680261954452</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.355631826138711</v>
+        <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.977582733943111</v>
+        <v>-3.100344711325025</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.164242308247719</v>
+        <v>1.212680645364417</v>
       </c>
       <c r="F1971" t="n">
         <v>0.51768037460316</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.666240050900607</v>
+        <v>2.763783178970071</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.425922058460886</v>
+        <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.904204636854375</v>
+        <v>-3.026966614236289</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.263883779405389</v>
+        <v>1.312322116522087</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5910584716918965</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.780557141476025</v>
+        <v>2.878100269545488</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.44054979457693</v>
+        <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.001945181479349</v>
+        <v>-3.124707158861263</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.239415297671443</v>
+        <v>1.287853634788141</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5751691935589163</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.78565131071228</v>
+        <v>2.883194438781744</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.439085775401602</v>
+        <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.178282941602278</v>
+        <v>-3.301044918984192</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.167416174446943</v>
+        <v>1.215854511563641</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3988314334359869</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.678384635463194</v>
+        <v>2.775927763532658</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.43757739344153</v>
+        <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.101860895170351</v>
+        <v>-3.224622872552266</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.196476611059642</v>
+        <v>1.24491494817634</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3988314334359869</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.676876253503123</v>
+        <v>2.774419381572586</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.437440260876966</v>
+        <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.057487763531783</v>
+        <v>-3.180249740913697</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.214088731150506</v>
+        <v>1.262527068267204</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4432045650745555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.7033629999217</v>
+        <v>2.800906127991164</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.431834055015557</v>
+        <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.934653542644615</v>
+        <v>-3.05741552002653</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.257616213643963</v>
+        <v>1.306054550760662</v>
       </c>
       <c r="F1977" t="n">
         <v>0.4432045650745555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.69775679406029</v>
+        <v>2.795299922129754</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.438215812043361</v>
+        <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.88699781208356</v>
+        <v>-3.009759789465474</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.28306026289619</v>
+        <v>1.331498600012888</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4908602956356112</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.732731989424728</v>
+        <v>2.830275117494192</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.443108185418086</v>
+        <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.786479653584805</v>
+        <v>-2.90924163096672</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.328159899670417</v>
+        <v>1.376598236787115</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5913784541343657</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.797935257898705</v>
+        <v>2.89547838596817</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.429862857893958</v>
+        <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.847146243987194</v>
+        <v>-2.969908221369109</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.290647935985333</v>
+        <v>1.339086273102032</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5096801374158321</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.735670940343458</v>
+        <v>2.833214068412922</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.433960560504587</v>
+        <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.802307842378796</v>
+        <v>-2.925069819760711</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.312680999239321</v>
+        <v>1.361119336356019</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5142235703607015</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.742494702721008</v>
+        <v>2.840037830790472</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.438121500135665</v>
+        <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.903066478135794</v>
+        <v>-3.025828455517709</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.2765384845676</v>
+        <v>1.324976821684298</v>
       </c>
       <c r="F1982" t="n">
         <v>0.4253980016336961</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.693360301115883</v>
+        <v>2.790903429185347</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.444001102663502</v>
+        <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.858863641049894</v>
+        <v>-2.981625618431809</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.300099221929797</v>
+        <v>1.348537559046495</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4696008387195966</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.72576160589526</v>
+        <v>2.823304733964724</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.442411103132749</v>
+        <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.895842668713337</v>
+        <v>-3.018604646095252</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.283717611333667</v>
+        <v>1.332155948450366</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5065747405109271</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.746355947439306</v>
+        <v>2.84389907550877</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.493658868315789</v>
+        <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.737551251174065</v>
+        <v>-2.86031322855598</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.398281943532416</v>
+        <v>1.446720280649114</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5065747405109271</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.797603712622346</v>
+        <v>2.89514684069181</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.492099572910042</v>
+        <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.529909247539589</v>
+        <v>-2.652671224921503</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.479779449580459</v>
+        <v>1.528217786697158</v>
       </c>
       <c r="F1986" t="n">
         <v>0.7142167441454033</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.920629619397284</v>
+        <v>3.018172747466749</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.487047801148312</v>
+        <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.478877154817061</v>
+        <v>-2.601639132198975</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.495140514907741</v>
+        <v>1.543578852024439</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7652488368679312</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.946197103269071</v>
+        <v>3.043740231338536</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.504235205241017</v>
+        <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.413652973689855</v>
+        <v>-2.53641495107177</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.538417591451328</v>
+        <v>1.586855928568026</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8304730179951368</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.002519016038099</v>
+        <v>3.100062144107564</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.500196177540297</v>
+        <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.376225953618721</v>
+        <v>-2.498987931000636</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.549349371779062</v>
+        <v>1.59778770889576</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8357245560243185</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.001630911154889</v>
+        <v>3.099174039224353</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.501452969871538</v>
+        <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.396337609653429</v>
+        <v>-2.519099587035344</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.542561501696419</v>
+        <v>1.590999838813117</v>
       </c>
       <c r="F1990" t="n">
         <v>0.8467519010217377</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.009504110484581</v>
+        <v>3.107047238554045</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.662010740892748</v>
+        <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.342592795226225</v>
+        <v>-2.465354772608139</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.724617198488511</v>
+        <v>1.77305553560521</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8568152104621997</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.176099867170068</v>
+        <v>3.273642995239533</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.782123650110566</v>
+        <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.318801226620082</v>
+        <v>-2.441563204001997</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.854246735148786</v>
+        <v>1.902685072265484</v>
       </c>
       <c r="F1992" t="n">
         <v>0.8806067790683419</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.310487717551571</v>
+        <v>3.408030845621036</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.773831626124425</v>
+        <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.292717142356274</v>
+        <v>-2.415479119738189</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.856388344868168</v>
+        <v>1.904826681984866</v>
       </c>
       <c r="F1993" t="n">
         <v>0.8806067790683419</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.30219569356543</v>
+        <v>3.399738821634894</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.772024821708204</v>
+        <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.214585961507328</v>
+        <v>-2.337347938889242</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.885834012791526</v>
+        <v>1.934272349908224</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9547835899520265</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.34489497567942</v>
+        <v>3.442438103748885</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.789579227434996</v>
+        <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.205693500114045</v>
+        <v>-2.328455477495959</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.906945403075631</v>
+        <v>1.955383740192329</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9547835899520265</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.362449381406212</v>
+        <v>3.459992509475676</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.78143427483958</v>
+        <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.374169617083922</v>
+        <v>-2.496931594465837</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.831410003692263</v>
+        <v>1.879848340808962</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9268357542354457</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.337535727380847</v>
+        <v>3.435078855450311</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.762703972027441</v>
+        <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.676370088222339</v>
+        <v>-1.799132065604254</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.091799512424759</v>
+        <v>2.140237849541457</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8564876948650351</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.276596588946463</v>
+        <v>3.374139717015927</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.753367994524346</v>
+        <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.653648984539187</v>
+        <v>-1.776410961921101</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.091551976394924</v>
+        <v>2.139990313511622</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8564876948650351</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.267260611443367</v>
+        <v>3.364803739512832</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.912274120375515</v>
+        <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.651923941249143</v>
+        <v>-1.774685918631058</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.251148119562111</v>
+        <v>2.299586456678809</v>
       </c>
       <c r="F1999" t="n">
         <v>0.8582127381550788</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.427201763268562</v>
+        <v>3.524744891338027</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.949351942869161</v>
+        <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.806704948027398</v>
+        <v>-1.929466925409313</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.226313539344455</v>
+        <v>2.274751876461154</v>
       </c>
       <c r="F2000" t="n">
         <v>0.8248450641006027</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.444258981329523</v>
+        <v>3.541802109398988</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.946027298858707</v>
+        <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.755269614642739</v>
+        <v>-1.878031592024653</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.243563028687864</v>
+        <v>2.292001365804563</v>
       </c>
       <c r="F2001" t="n">
         <v>0.8762803974852623</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.471795537349864</v>
+        <v>3.569338665419329</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.956033452503448</v>
+        <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.728318390316251</v>
+        <v>-1.851080367698165</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.264349672063201</v>
+        <v>2.312788009179899</v>
       </c>
       <c r="F2002" t="n">
         <v>0.8911607435129815</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.490729898611237</v>
+        <v>3.588273026680702</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.140136584648408</v>
+        <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.864271398372567</v>
+        <v>-1.987033375754481</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.394071600985634</v>
+        <v>2.442509938102333</v>
       </c>
       <c r="F2003" t="n">
         <v>0.8911607435129815</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.674833030756197</v>
+        <v>3.772376158825661</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.132253279551401</v>
+        <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.886679516177439</v>
+        <v>-2.009441493559353</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.377225048766678</v>
+        <v>2.425663385883377</v>
       </c>
       <c r="F2004" t="n">
         <v>0.8911607435129815</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.66694972565919</v>
+        <v>3.764492853728655</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.134307279101038</v>
+        <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.034685283656838</v>
+        <v>-2.157447261038753</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.320076741324556</v>
+        <v>2.368515078441254</v>
       </c>
       <c r="F2005" t="n">
         <v>0.80443373464944</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.616967519890703</v>
+        <v>3.714510647960167</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.190560996822886</v>
+        <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.044126209545368</v>
+        <v>-2.166888186927283</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.372554088690991</v>
+        <v>2.42099242580769</v>
       </c>
       <c r="F2006" t="n">
         <v>0.9268608521928314</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.746677508138585</v>
+        <v>3.844220636208049</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.193452091368187</v>
+        <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.042839446005812</v>
+        <v>-2.165601423387726</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.375959888652114</v>
+        <v>2.424398225768813</v>
       </c>
       <c r="F2007" t="n">
         <v>0.928147615732388</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.75034066080762</v>
+        <v>3.847883788877084</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.191563904261962</v>
+        <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.044396499995103</v>
+        <v>-2.167158477377018</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.373448879950173</v>
+        <v>2.421887217066872</v>
       </c>
       <c r="F2008" t="n">
         <v>0.928147615732388</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.748452473701395</v>
+        <v>3.845995601770859</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.186384133864824</v>
+        <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.051668385518568</v>
+        <v>-2.174430362900482</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.36536035534365</v>
+        <v>2.413798692460348</v>
       </c>
       <c r="F2009" t="n">
         <v>0.9208757302089232</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.738909571990178</v>
+        <v>3.836452700059643</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.184818144074976</v>
+        <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.049827366460316</v>
+        <v>-2.172589343842231</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.364530773177103</v>
+        <v>2.412969110293801</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9221439568803916</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.738104518203212</v>
+        <v>3.835647646272676</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.197891550940895</v>
+        <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.056736071959997</v>
+        <v>-2.179498049341912</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.374840697843149</v>
+        <v>2.423279034959847</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9221439568803916</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.75117792506913</v>
+        <v>3.848721053138594</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.197891550940895</v>
+        <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.058297714774857</v>
+        <v>-2.181059692156771</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.374216040717205</v>
+        <v>2.422654377833903</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9221439568803916</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.75117792506913</v>
+        <v>3.848721053138594</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.196415592067897</v>
+        <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.08619850188433</v>
+        <v>-2.208960479266244</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.361579767000418</v>
+        <v>2.410018104117116</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8875470327374568</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.728943811710371</v>
+        <v>3.826486939779835</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.193180036045096</v>
+        <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.089231499397004</v>
+        <v>-2.211993476778918</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.357131011972547</v>
+        <v>2.405569349089245</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8845140352247829</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.723888457179966</v>
+        <v>3.82143158524943</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.259885995635599</v>
+        <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.10929282067351</v>
+        <v>-2.232054798055425</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.415812443052448</v>
+        <v>2.464250780169146</v>
       </c>
       <c r="F2015" t="n">
         <v>0.8644527139482758</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.778557624004565</v>
+        <v>3.876100752074029</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.400197714637446</v>
+        <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.366013638668334</v>
+        <v>-2.488775616050249</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.453435834856366</v>
+        <v>2.501874171973064</v>
       </c>
       <c r="F2016" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.853820598520123</v>
+        <v>3.951363726589587</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.469177983783086</v>
+        <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.520000056444475</v>
+        <v>-2.64276203382639</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.460821536891549</v>
+        <v>2.509259874008247</v>
       </c>
       <c r="F2017" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.922800867665763</v>
+        <v>4.020343995735227</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.455229185903207</v>
+        <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.469478152616809</v>
+        <v>-2.592240129998724</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.467081500542736</v>
+        <v>2.515519837659435</v>
       </c>
       <c r="F2018" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.908852069785884</v>
+        <v>4.006395197855348</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.467099674958621</v>
+        <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.721953306624534</v>
+        <v>-2.844715284006448</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.37796192799506</v>
+        <v>2.426400265111759</v>
       </c>
       <c r="F2019" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.920722558841298</v>
+        <v>4.018265686910762</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.468310209477565</v>
+        <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.991426108546242</v>
+        <v>-3.114188085928157</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.271383341745321</v>
+        <v>2.319821678862019</v>
       </c>
       <c r="F2020" t="n">
         <v>0.756038139804461</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.921933093360241</v>
+        <v>4.019476221429706</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637087</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.472431951704886</v>
+        <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.148970180275683</v>
+        <v>-3.271732157657598</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.212487455280866</v>
+        <v>2.260925792397564</v>
       </c>
       <c r="F2021" t="n">
         <v>0.6891363346641866</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.885913752503399</v>
+        <v>3.983456880572863</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.846892850544258</v>
+        <v>3.760750896680999</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.879810186185204</v>
+        <v>3.662196351556567</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.148970180275683</v>
+        <v>-3.271732157657598</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.212487455280866</v>
+        <v>2.260925792397564</v>
       </c>
       <c r="F2022" t="n">
         <v>0.6891363346641866</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.872873983171571</v>
+        <v>3.655260148542935</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240711.xlsx
+++ b/tame_output/ON/bt/strategyON_20240711.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>45.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.4%</t>
+          <t>121.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.4%</t>
+          <t>-66.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.8%</t>
+          <t>457.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-488.7%</t>
+          <t>-490.5%</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-35.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.1%</t>
+          <t>-150.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-125.7%</t>
+          <t>-115.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-155.1%</t>
+          <t>-166.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,42 +1456,42 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-89.9%</t>
         </is>
       </c>
     </row>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-6.63075194709096</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.4662214905425572</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.995118069805685</v>
+        <v>-6.836002966327721</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3165746066023623</v>
+        <v>0.3802206479935482</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.158697947990069</v>
+        <v>-6.999582844512105</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2495475753836098</v>
+        <v>0.3131936167747953</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.455359289800266</v>
+        <v>-7.296244186322302</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1346620145887392</v>
+        <v>0.1983080559799246</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.642078998109569</v>
+        <v>-7.482963894631605</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.05594782673061482</v>
+        <v>0.1195938681218003</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.025080386852199</v>
+        <v>-7.865965283374236</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.09735483008802115</v>
+        <v>-0.03370878869683613</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.206950177837234</v>
+        <v>-8.047835074359272</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1675312305106051</v>
+        <v>-0.1038851891194201</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.340154467722146</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.566480500341235</v>
+        <v>-8.407365396863273</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.3059930562141555</v>
+        <v>-0.2423470148229705</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.340154467722146</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.616829563795458</v>
+        <v>-8.457714460317495</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3182166616386666</v>
+        <v>-0.254570620247482</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.390503531176368</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.714448841216853</v>
+        <v>-8.555333737738891</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3542226219854565</v>
+        <v>-0.2905765805942715</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.488122808597764</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.861974929222496</v>
+        <v>-8.702859825744534</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.4103395008661415</v>
+        <v>-0.3466934594749564</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.635648896603408</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.06623310455236</v>
+        <v>-8.907118001074398</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4865295738794444</v>
+        <v>-0.4228835324882594</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.763287841217397</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.099885943060833</v>
+        <v>-8.940770839582871</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4955081547983977</v>
+        <v>-0.4318621134072127</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.863701209134434</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.026416111393385</v>
+        <v>-8.867301007915422</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.4507485206379971</v>
+        <v>-0.3871024792468121</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.790231377466986</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.201540528779928</v>
+        <v>-9.042425425301966</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.5062430668450975</v>
+        <v>-0.4425970254539129</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.965355794853529</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.435992622794418</v>
+        <v>-9.276877519316455</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.6072430693524895</v>
+        <v>-0.5435970279613045</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.965355794853529</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.540367353820864</v>
+        <v>-9.381252250342902</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6556651525370443</v>
+        <v>-0.5920191111458593</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.069730525879975</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.593153509421191</v>
+        <v>-9.434038405943229</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6756638249386184</v>
+        <v>-0.6120177835474339</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.165406012462372</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.71919030278948</v>
+        <v>-9.560075199311518</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.7233848136568195</v>
+        <v>-0.6597387722656349</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.14015438965263</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.662118530893549</v>
+        <v>-9.503003427415587</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6965657692120466</v>
+        <v>-0.6329197278208616</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.14015438965263</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.803790372617669</v>
+        <v>-9.644675269139707</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7547097328004364</v>
+        <v>-0.6910636914092514</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.14015438965263</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.754199528192835</v>
+        <v>-9.595084424714873</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7198199848656301</v>
+        <v>-0.6561739434744456</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.090563545227796</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.605281193720979</v>
+        <v>-9.446166090243016</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6733037847235708</v>
+        <v>-0.6096577433323858</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.059313954492623</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.379436041001568</v>
+        <v>-9.220320937523606</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5733866505995979</v>
+        <v>-0.5097406092084129</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.017387278905459</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.254857384663977</v>
+        <v>-9.095742281186014</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5224160435085023</v>
+        <v>-0.4587700021173173</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.017387278905459</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.307752672708263</v>
+        <v>-9.148637569230301</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.5409403845641094</v>
+        <v>-0.4772943431729244</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.012431932817013</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.235619497420382</v>
+        <v>-9.07650439394242</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5063534102103202</v>
+        <v>-0.4427073688191356</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.012431932817013</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.164253104810735</v>
+        <v>-9.005138001332773</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4875441155603264</v>
+        <v>-0.4238980741691418</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.941065540207365</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.07079407082551</v>
+        <v>-8.911678967347548</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.4600439832791445</v>
+        <v>-0.3963979418879595</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.941065540207365</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.803552269957112</v>
+        <v>-8.64443716647915</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3549818234311588</v>
+        <v>-0.2913357820399742</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.941065540207365</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.705645231280622</v>
+        <v>-8.54653012780266</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3161193229340236</v>
+        <v>-0.2524732815428385</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.873079790346809</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.681691690304664</v>
+        <v>-8.522576586826702</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3058694003981466</v>
+        <v>-0.242223359006962</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.849126249370851</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.417631751981867</v>
+        <v>-8.258516648503905</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2135057412307804</v>
+        <v>-0.1498596998395954</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.585066311048055</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.710552128477029</v>
+        <v>-7.551437024999067</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.06653907451085406</v>
+        <v>0.1301851159020391</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.585066311048055</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.670367830110838</v>
+        <v>-7.511252726632876</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.0829564177451716</v>
+        <v>0.1466024591363566</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.544882012681864</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.506967959171476</v>
+        <v>-7.347852855693514</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1476831873416735</v>
+        <v>0.2113292287328585</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.381482141742502</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.273486736941877</v>
+        <v>-7.114371633463915</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2490001050713655</v>
+        <v>0.3126461464625505</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.148000919512903</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.123820345934362</v>
+        <v>-6.9647052424564</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3059744511614122</v>
+        <v>0.3696204925525972</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.055097428270367</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.991544872303476</v>
+        <v>-6.832429768825514</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3542521273607941</v>
+        <v>0.4178981687519787</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.9228219546394807</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.835806539743734</v>
+        <v>-6.676691436265772</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4193625210723275</v>
+        <v>0.4830085624635121</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.7670836220797391</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.586806741060153</v>
+        <v>-6.427691637582191</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5318687817694188</v>
+        <v>0.5955148231606033</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.7670836220797391</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.692396730833257</v>
+        <v>-6.533281627355295</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3616568562609581</v>
+        <v>0.4253028976521431</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.8726736118528435</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.711131632951854</v>
+        <v>-6.552016529473892</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4027072372906058</v>
+        <v>0.4663532786817903</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.8782696215129748</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.563191591544255</v>
+        <v>-6.404076488066293</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3420043311654779</v>
+        <v>0.4056503725566625</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.8579487056044173</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.510222069290267</v>
+        <v>-6.351106965812304</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.354478153813595</v>
+        <v>0.4181241952047801</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.8049791833504284</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.466673662519576</v>
+        <v>-6.307558559041614</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3649369044267781</v>
+        <v>0.4285829458179631</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.8049791833504284</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.224525269065718</v>
+        <v>-6.065410165587756</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4762586161894644</v>
+        <v>0.5399046575806494</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.8049791833504284</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.116266131943196</v>
+        <v>-5.957151028465234</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5140943914976681</v>
+        <v>0.5777404328888531</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.8049791833504284</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.992974997126066</v>
+        <v>-5.833859893648103</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5609089394350972</v>
+        <v>0.6245549808262822</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.6816880485332979</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.971825798222622</v>
+        <v>-5.81271069474466</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5770695972338</v>
+        <v>0.6407156386249846</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.6605388496298545</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.728060356239178</v>
+        <v>-5.568945252761216</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6703564823742285</v>
+        <v>0.7340025237654131</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.6605388496298545</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.626297535961883</v>
+        <v>-5.467182432483921</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7131859244051624</v>
+        <v>0.7768319657963469</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.6473197812374258</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.376447142012808</v>
+        <v>-5.217332038534846</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8058681569684945</v>
+        <v>0.869514198359679</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.6473197812374258</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.200555049545375</v>
+        <v>-5.041439946067413</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8798241174761161</v>
+        <v>0.9434701588673011</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.6473197812374258</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.029108586522912</v>
+        <v>-4.86999348304495</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9617302087396551</v>
+        <v>1.02537625013084</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.4758733182149627</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.954819020784573</v>
+        <v>-4.795703917306611</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9904665126512879</v>
+        <v>1.054112554042473</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.4015837524766234</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.891183278550638</v>
+        <v>-4.732068175072676</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.020615610599179</v>
+        <v>1.084261651990364</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.3379480102426889</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.779756519224718</v>
+        <v>-4.620641415746756</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.046380573113343</v>
+        <v>1.110026614504527</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.3379480102426889</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.539326022419858</v>
+        <v>-4.380210918941896</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.144295848460164</v>
+        <v>1.207941889851349</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.09751751343782861</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.344732585605771</v>
+        <v>-4.307968350770701</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.226062537020619</v>
+        <v>1.240768230954647</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.09751751343782861</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.291734263324384</v>
+        <v>-4.254970028489313</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.247940449850514</v>
+        <v>1.262646143784542</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.04218125443588977</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.182929377844657</v>
+        <v>-4.146165143009586</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.288460475262398</v>
+        <v>1.303166169196426</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.04218125443588977</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.962908579807646</v>
+        <v>-3.926144344972575</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.378047831487817</v>
+        <v>1.392753525421845</v>
       </c>
       <c r="F1929" t="n">
         <v>0.09903859063209047</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.830040890744367</v>
+        <v>-3.793276655909297</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.447089089914952</v>
+        <v>1.46179478384898</v>
       </c>
       <c r="F1930" t="n">
         <v>0.09903859063209047</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.709867807379869</v>
+        <v>-3.673103572544798</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.496304167701053</v>
+        <v>1.511009861635081</v>
       </c>
       <c r="F1931" t="n">
         <v>0.2192116739965894</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.565195662280131</v>
+        <v>-3.528431427445061</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.564261128302388</v>
+        <v>1.578966822236416</v>
       </c>
       <c r="F1932" t="n">
         <v>0.3638838190963268</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.625070489637824</v>
+        <v>-3.588306254802753</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.526348688760736</v>
+        <v>1.541054382694765</v>
       </c>
       <c r="F1933" t="n">
         <v>0.3040089917386347</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.505250258726986</v>
+        <v>-3.468486023891916</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.58956595035928</v>
+        <v>1.604271644293308</v>
       </c>
       <c r="F1934" t="n">
         <v>0.3040089917386347</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.507719965188792</v>
+        <v>-3.470955730353722</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.496222267096999</v>
+        <v>1.510927961031027</v>
       </c>
       <c r="F1935" t="n">
         <v>0.3015392852768286</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.576090151512802</v>
+        <v>-3.539325916677732</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.388136054052697</v>
+        <v>1.402841747986725</v>
       </c>
       <c r="F1936" t="n">
         <v>0.3108149843130435</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.589878204359849</v>
+        <v>-3.553113969524778</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.373057541545769</v>
+        <v>1.387763235479798</v>
       </c>
       <c r="F1937" t="n">
         <v>0.3108149843130435</v>
@@ -46125,10 +46125,10 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.620871363688554</v>
+        <v>-3.584107128853484</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.185369842854674</v>
+        <v>1.200075536788702</v>
       </c>
       <c r="F1938" t="n">
         <v>0.3108149843130435</v>
@@ -46148,10 +46148,10 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.445397103896085</v>
+        <v>-3.408632869061015</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.260126778763449</v>
+        <v>1.274832472697478</v>
       </c>
       <c r="F1939" t="n">
         <v>0.3108149843130435</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.556333356537333</v>
+        <v>-3.519569121702263</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.191494306468157</v>
+        <v>1.206200000402185</v>
       </c>
       <c r="F1940" t="n">
         <v>0.3108149843130435</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.522669811065052</v>
+        <v>-3.485905576229981</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.208091109876975</v>
+        <v>1.222796803811004</v>
       </c>
       <c r="F1941" t="n">
         <v>0.3444785297853253</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.462817191861328</v>
+        <v>-3.426052957026258</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.242204543990597</v>
+        <v>1.256910237924625</v>
       </c>
       <c r="F1942" t="n">
         <v>0.3444785297853253</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.376573728834951</v>
+        <v>-3.339809493999881</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.271648199775008</v>
+        <v>1.286353893709036</v>
       </c>
       <c r="F1943" t="n">
         <v>0.3444785297853253</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.421880548233931</v>
+        <v>-3.385116313398861</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.245301247459942</v>
+        <v>1.26000694139397</v>
       </c>
       <c r="F1944" t="n">
         <v>0.3036683667760945</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.450913652936233</v>
+        <v>-3.414149418101162</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.234239878612123</v>
+        <v>1.248945572546151</v>
       </c>
       <c r="F1945" t="n">
         <v>0.3036683667760945</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.358103171485373</v>
+        <v>-3.321338936650303</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.200636763083832</v>
+        <v>1.21534245701786</v>
       </c>
       <c r="F1946" t="n">
         <v>0.3964788482269539</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.402492640814801</v>
+        <v>-3.365728405979731</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.184754451276662</v>
+        <v>1.19946014521069</v>
       </c>
       <c r="F1947" t="n">
         <v>0.3520893788975262</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.289821422578551</v>
+        <v>-3.25305718774348</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.224898647082885</v>
+        <v>1.239604341016913</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4647605971337764</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.177444421395878</v>
+        <v>-3.140680186560808</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.275340743386621</v>
+        <v>1.290046437320649</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4647605971337764</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.205224819297231</v>
+        <v>-3.168460584462161</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.275725785994619</v>
+        <v>1.290431479928647</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4369801992324234</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.28822610032251</v>
+        <v>-3.25146186548744</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.080880993585161</v>
+        <v>1.095586687519189</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4184093147052496</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.396840178765841</v>
+        <v>-3.360075943930771</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.157585022927034</v>
+        <v>1.172290716861062</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4184093147052496</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.361431140517698</v>
+        <v>-3.324666905682628</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.186261664328614</v>
+        <v>1.200967358262642</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4184093147052496</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.323047477959547</v>
+        <v>-3.286283243124477</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.199034570694243</v>
+        <v>1.213740264628271</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4567929772634008</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.145931147924381</v>
+        <v>-3.109166913089311</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.266610131553612</v>
+        <v>1.28131582548764</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4567929772634008</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.191023392757927</v>
+        <v>-3.154259157922857</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.249256625382107</v>
+        <v>1.263962319316135</v>
       </c>
       <c r="F1956" t="n">
         <v>0.394896934094011</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.011647971519159</v>
+        <v>-3.029019991416763</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.314793769184028</v>
+        <v>1.307844961224987</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5516736922647296</v>
+        <v>0.4339184020500682</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.850813597464277</v>
+        <v>2.78016042333548</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.056662185039766</v>
+        <v>-3.074034204937369</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.277595539107375</v>
+        <v>1.270646731148334</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.521324796950125</v>
+        <v>0.4035695067354636</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.813411715607104</v>
+        <v>2.742758541478307</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.323666695312201</v>
+        <v>-3.341038715209804</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.176485297337347</v>
+        <v>1.169536489378306</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3269617589071764</v>
+        <v>0.209206468692515</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.702485455120281</v>
+        <v>2.631832280991484</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.424864476749374</v>
+        <v>-3.442236496646977</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.135210106658979</v>
+        <v>1.128261298699938</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2585529453618572</v>
+        <v>0.1407976551471958</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.660644088889591</v>
+        <v>2.589990914760794</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.418353510135061</v>
+        <v>-3.435725530032665</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.135414454859021</v>
+        <v>1.12846564689998</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2585529453618572</v>
+        <v>0.1407976551471958</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.658244050443908</v>
+        <v>2.587590876315111</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.399315382427764</v>
+        <v>-3.416687402325367</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.139554425150185</v>
+        <v>1.132605617191144</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2003693340306627</v>
+        <v>0.08261404381600129</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.619858602853436</v>
+        <v>2.549205428724639</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.430442013578382</v>
+        <v>-3.447814033475985</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.304685641628618</v>
+        <v>1.297736833669577</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2003693340306627</v>
+        <v>0.08261404381600129</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.797440471792116</v>
+        <v>2.72678729766332</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.444308774912299</v>
+        <v>-3.461680794809903</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.299972266081185</v>
+        <v>1.293023458122144</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1625114172968398</v>
+        <v>0.04475612708217835</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.775559050737956</v>
+        <v>2.704905876609159</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.399504603372369</v>
+        <v>-3.416876623269973</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.323902465094083</v>
+        <v>1.316953657135042</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1625114172968398</v>
+        <v>0.04475612708217835</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.781567581134882</v>
+        <v>2.710914407006085</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.251761633137367</v>
+        <v>-3.269133653034971</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.280949874465283</v>
+        <v>1.274001066506242</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3303187745317229</v>
+        <v>0.2125634843170615</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.780202216753011</v>
+        <v>2.709549042624214</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.353776315668588</v>
+        <v>-3.371148335566192</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.242937622984276</v>
+        <v>1.235988815025234</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3303187745317229</v>
+        <v>0.2125634843170615</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.782995838284492</v>
+        <v>2.712342664155695</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.347623609615804</v>
+        <v>-3.364995629513407</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.246061053797048</v>
+        <v>1.239112245838007</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3364714805845072</v>
+        <v>0.2187161903698458</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.787349810307821</v>
+        <v>2.716696636179024</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.364432907766305</v>
+        <v>-3.381804927663909</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.238417811276958</v>
+        <v>1.231469003317916</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3196621824340056</v>
+        <v>0.2019068922193442</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.776344708157631</v>
+        <v>2.705691534028834</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.302134908990183</v>
+        <v>-3.319506928887787</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.329672564584227</v>
+        <v>1.322723756625186</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3196621824340056</v>
+        <v>0.2019068922193442</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.842680261954452</v>
+        <v>2.772027087825655</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.100344711325025</v>
+        <v>-3.117716731222629</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.212680645364417</v>
+        <v>1.205731837405376</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.51768037460316</v>
+        <v>0.3999250843884986</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.763783178970071</v>
+        <v>2.693130004841274</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.026966614236289</v>
+        <v>-3.044338634133892</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.312322116522087</v>
+        <v>1.305373308563046</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5910584716918965</v>
+        <v>0.4733031814772351</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.878100269545488</v>
+        <v>2.807447095416691</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.124707158861263</v>
+        <v>-3.142079178758867</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.287853634788141</v>
+        <v>1.2809048268291</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5751691935589163</v>
+        <v>0.4574139033442549</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.883194438781744</v>
+        <v>2.812541264652947</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.301044918984192</v>
+        <v>-3.318416938881796</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.215854511563641</v>
+        <v>1.2089057036046</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3988314334359869</v>
+        <v>0.2810761432213255</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.775927763532658</v>
+        <v>2.705274589403861</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.224622872552266</v>
+        <v>-3.241994892449869</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.24491494817634</v>
+        <v>1.237966140217299</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3988314334359869</v>
+        <v>0.2810761432213255</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.774419381572586</v>
+        <v>2.70376620744379</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.180249740913697</v>
+        <v>-3.1976217608113</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.262527068267204</v>
+        <v>1.255578260308163</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4432045650745555</v>
+        <v>0.3254492748598941</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.800906127991164</v>
+        <v>2.730252953862367</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.05741552002653</v>
+        <v>-3.074787539924133</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.306054550760662</v>
+        <v>1.29910574280162</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4432045650745555</v>
+        <v>0.3254492748598941</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.795299922129754</v>
+        <v>2.724646748000958</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.009759789465474</v>
+        <v>-3.027131809363078</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.331498600012888</v>
+        <v>1.324549792053847</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4908602956356112</v>
+        <v>0.3731050054209498</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.830275117494192</v>
+        <v>2.759621943365395</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.90924163096672</v>
+        <v>-2.926613650864323</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.376598236787115</v>
+        <v>1.369649428828074</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5913784541343657</v>
+        <v>0.4736231639197043</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.89547838596817</v>
+        <v>2.824825211839373</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.969908221369109</v>
+        <v>-2.987280241266712</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.339086273102032</v>
+        <v>1.33213746514299</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5096801374158321</v>
+        <v>0.3919248472011707</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.833214068412922</v>
+        <v>2.762560894284125</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.925069819760711</v>
+        <v>-2.942441839658314</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.361119336356019</v>
+        <v>1.354170528396978</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5142235703607015</v>
+        <v>0.3964682801460401</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.840037830790472</v>
+        <v>2.769384656661675</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917052</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.025828455517709</v>
+        <v>-3.043200475415313</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.324976821684298</v>
+        <v>1.318028013725257</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4253980016336961</v>
+        <v>0.3076427114190347</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.790903429185347</v>
+        <v>2.72025025505655</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.82668474540596</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.981625618431809</v>
+        <v>-2.998997638329412</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.348537559046495</v>
+        <v>1.341588751087454</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4696008387195966</v>
+        <v>0.3518455485049352</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.823304733964724</v>
+        <v>2.752651559835928</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.018604646095252</v>
+        <v>-3.035976665992855</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.332155948450366</v>
+        <v>1.325207140491324</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5065747405109271</v>
+        <v>0.3888194502962657</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.84389907550877</v>
+        <v>2.773245901379974</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.86031322855598</v>
+        <v>-2.877685248453583</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.446720280649114</v>
+        <v>1.439771472690073</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5065747405109271</v>
+        <v>0.3888194502962657</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.89514684069181</v>
+        <v>2.824493666563013</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.652671224921503</v>
+        <v>-2.670043244819107</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.528217786697158</v>
+        <v>1.521268978738116</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7142167441454033</v>
+        <v>0.5964614539307418</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.018172747466749</v>
+        <v>2.947519573337952</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.601639132198975</v>
+        <v>-2.619011152096579</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.543578852024439</v>
+        <v>1.536630044065398</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7652488368679312</v>
+        <v>0.6474935466532697</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.043740231338536</v>
+        <v>2.973087057209739</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.53641495107177</v>
+        <v>-2.553786970969373</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.586855928568026</v>
+        <v>1.579907120608985</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8304730179951368</v>
+        <v>0.7127177277804754</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.100062144107564</v>
+        <v>3.029408969978767</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.498987931000636</v>
+        <v>-2.516359950898239</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.59778770889576</v>
+        <v>1.590838900936719</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8357245560243185</v>
+        <v>0.717969265809657</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.099174039224353</v>
+        <v>3.028520865095556</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.519099587035344</v>
+        <v>-2.536471606932948</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.590999838813117</v>
+        <v>1.584051030854076</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8467519010217377</v>
+        <v>0.7289966108070762</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.107047238554045</v>
+        <v>3.036394064425248</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.465354772608139</v>
+        <v>-2.482726792505743</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.77305553560521</v>
+        <v>1.766106727646168</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8568152104621997</v>
+        <v>0.7390599202475382</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.273642995239533</v>
+        <v>3.202989821110736</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.441563204001997</v>
+        <v>-2.458935223899601</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.902685072265484</v>
+        <v>1.895736264306443</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.8806067790683419</v>
+        <v>0.7628514888536805</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.408030845621036</v>
+        <v>3.337377671492239</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.415479119738189</v>
+        <v>-2.432851139635793</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.904826681984866</v>
+        <v>1.897877874025825</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.8806067790683419</v>
+        <v>0.7628514888536805</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.399738821634894</v>
+        <v>3.329085647506098</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.337347938889242</v>
+        <v>-2.354719958786846</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.934272349908224</v>
+        <v>1.927323541949183</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9547835899520265</v>
+        <v>0.837028299737365</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.442438103748885</v>
+        <v>3.371784929620088</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.328455477495959</v>
+        <v>-2.345827497393563</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.955383740192329</v>
+        <v>1.948434932233288</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9547835899520265</v>
+        <v>0.837028299737365</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.459992509475676</v>
+        <v>3.389339335346879</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.496931594465837</v>
+        <v>-2.514303614363441</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.879848340808962</v>
+        <v>1.87289953284992</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9268357542354457</v>
+        <v>0.8090804640207843</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.435078855450311</v>
+        <v>3.364425681321515</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.799132065604254</v>
+        <v>-1.816504085501857</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.140237849541457</v>
+        <v>2.133289041582415</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8564876948650351</v>
+        <v>0.7387324046503736</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.374139717015927</v>
+        <v>3.30348654288713</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.776410961921101</v>
+        <v>-1.793782981818705</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.139990313511622</v>
+        <v>2.133041505552581</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8564876948650351</v>
+        <v>0.7387324046503736</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.364803739512832</v>
+        <v>3.294150565384035</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.774685918631058</v>
+        <v>-1.792057938528661</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.299586456678809</v>
+        <v>2.292637648719768</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8582127381550788</v>
+        <v>0.7404574479404173</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.524744891338027</v>
+        <v>3.45409171720923</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.929466925409313</v>
+        <v>-1.946838945306916</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.274751876461154</v>
+        <v>2.267803068502112</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8248450641006027</v>
+        <v>0.7070897738859412</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.541802109398988</v>
+        <v>3.471148935270191</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.878031592024653</v>
+        <v>-1.895403611922257</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.292001365804563</v>
+        <v>2.285052557845521</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8762803974852623</v>
+        <v>0.7585251072706009</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.569338665419329</v>
+        <v>3.498685491290532</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.851080367698165</v>
+        <v>-1.868452387595769</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.312788009179899</v>
+        <v>2.305839201220858</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8911607435129815</v>
+        <v>0.77340545329832</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.588273026680702</v>
+        <v>3.517619852551905</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.987033375754481</v>
+        <v>-2.004405395652085</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.442509938102333</v>
+        <v>2.435561130143291</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8911607435129815</v>
+        <v>0.77340545329832</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.772376158825661</v>
+        <v>3.701722984696865</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.009441493559353</v>
+        <v>-2.026813513456957</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.425663385883377</v>
+        <v>2.418714577924336</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8911607435129815</v>
+        <v>0.77340545329832</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.764492853728655</v>
+        <v>3.693839679599858</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.157447261038753</v>
+        <v>-2.174819280936356</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.368515078441254</v>
+        <v>2.361566270482213</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.80443373464944</v>
+        <v>0.6866784444347785</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.714510647960167</v>
+        <v>3.64385747383137</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.166888186927283</v>
+        <v>-2.184260206824886</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.42099242580769</v>
+        <v>2.414043617848648</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9268608521928314</v>
+        <v>0.80910556197817</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.844220636208049</v>
+        <v>3.773567462079252</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.165601423387726</v>
+        <v>-2.18297344328533</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.424398225768813</v>
+        <v>2.417449417809772</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.928147615732388</v>
+        <v>0.8103923255177266</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.847883788877084</v>
+        <v>3.777230614748287</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.167158477377018</v>
+        <v>-2.184530497274621</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.421887217066872</v>
+        <v>2.414938409107831</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.928147615732388</v>
+        <v>0.8103923255177266</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.845995601770859</v>
+        <v>3.775342427642062</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.174430362900482</v>
+        <v>-2.191802382798086</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.413798692460348</v>
+        <v>2.406849884501307</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9208757302089232</v>
+        <v>0.8031204399942617</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.836452700059643</v>
+        <v>3.765799525930845</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.172589343842231</v>
+        <v>-2.189961363739835</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.412969110293801</v>
+        <v>2.40602030233476</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9221439568803916</v>
+        <v>0.8043886666657302</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.835647646272676</v>
+        <v>3.764994472143879</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.179498049341912</v>
+        <v>-2.196870069239515</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.423279034959847</v>
+        <v>2.416330227000806</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9221439568803916</v>
+        <v>0.8043886666657302</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.848721053138594</v>
+        <v>3.778067879009797</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763532</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.181059692156771</v>
+        <v>-2.198431712054375</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.422654377833903</v>
+        <v>2.415705569874862</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9221439568803916</v>
+        <v>0.8043886666657302</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.848721053138594</v>
+        <v>3.778067879009797</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.208960479266244</v>
+        <v>-2.226332499163848</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.410018104117116</v>
+        <v>2.403069296158075</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8875470327374568</v>
+        <v>0.7697917425227954</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.826486939779835</v>
+        <v>3.755833765651039</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.211993476778918</v>
+        <v>-2.229365496676522</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.405569349089245</v>
+        <v>2.398620541130204</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8845140352247829</v>
+        <v>0.7667587450101214</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.82143158524943</v>
+        <v>3.750778411120633</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.232054798055425</v>
+        <v>-2.249426817953029</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.464250780169146</v>
+        <v>2.457301972210105</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8644527139482758</v>
+        <v>0.7466974237336144</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.876100752074029</v>
+        <v>3.805447577945233</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.488775616050249</v>
+        <v>-2.506147635947853</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.501874171973064</v>
+        <v>2.494925364014023</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.756038139804461</v>
+        <v>0.6382828495897995</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.951363726589587</v>
+        <v>3.880710552460791</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.64276203382639</v>
+        <v>-2.660134053723993</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.509259874008247</v>
+        <v>2.502311066049206</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.756038139804461</v>
+        <v>0.6382828495897995</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.020343995735227</v>
+        <v>3.94969082160643</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.592240129998724</v>
+        <v>-2.609612149896327</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.515519837659435</v>
+        <v>2.508571029700393</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.756038139804461</v>
+        <v>0.6382828495897995</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.006395197855348</v>
+        <v>3.935742023726552</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.844715284006448</v>
+        <v>-2.862087303904052</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.426400265111759</v>
+        <v>2.419451457152717</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.756038139804461</v>
+        <v>0.6382828495897995</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.018265686910762</v>
+        <v>3.947612512781966</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.114188085928157</v>
+        <v>-3.13156010582576</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.319821678862019</v>
+        <v>2.312872870902978</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.756038139804461</v>
+        <v>0.6382828495897995</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.019476221429706</v>
+        <v>3.948823047300909</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.271732157657598</v>
+        <v>-3.289104177555201</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.260925792397564</v>
+        <v>2.253976984438523</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6891363346641866</v>
+        <v>0.5713810444495251</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.983456880572863</v>
+        <v>3.912803706444066</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.760750896680999</v>
+        <v>3.818754475057874</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.662196351556567</v>
+        <v>3.567724630067084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.271732157657598</v>
+        <v>-3.289104177555201</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.260925792397564</v>
+        <v>2.253976984438523</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6891363346641866</v>
+        <v>0.5713810444495251</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.655260148542935</v>
+        <v>3.560788427053451</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240711.xlsx
+++ b/tame_output/ON/bt/strategyON_20240711.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.5%</t>
+          <t>122.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>-66.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.5%</t>
+          <t>457.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-490.5%</t>
+          <t>-501.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.8%</t>
+          <t>-155.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-115.3%</t>
+          <t>-125.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.9%</t>
+          <t>-171.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,42 +1456,42 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-89.9%</t>
+          <t>-58.2%</t>
         </is>
       </c>
     </row>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.63075194709096</v>
+        <v>-6.626873253827722</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4662214905425572</v>
+        <v>0.4677729678478526</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.836002966327721</v>
+        <v>-6.722400026520157</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3802206479935482</v>
+        <v>0.4256618239165735</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.999582844512105</v>
+        <v>-6.885979904704541</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3131936167747953</v>
+        <v>0.3586347926978211</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.296244186322302</v>
+        <v>-7.182641246514739</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1983080559799246</v>
+        <v>0.2437492319029499</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.482963894631605</v>
+        <v>-7.369360954824042</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1195938681218003</v>
+        <v>0.1650350440448261</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.865965283374236</v>
+        <v>-7.752362343566673</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.03370878869683613</v>
+        <v>0.01173238722618919</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.047835074359272</v>
+        <v>-7.934232134551708</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1038851891194201</v>
+        <v>-0.05844401319639481</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.340154467722146</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.407365396863273</v>
+        <v>-8.29376245705571</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2423470148229705</v>
+        <v>-0.1969058388999452</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.340154467722146</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.457714460317495</v>
+        <v>-8.344111520509932</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.254570620247482</v>
+        <v>-0.2091294443244567</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.390503531176368</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.555333737738891</v>
+        <v>-8.441730797931328</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2905765805942715</v>
+        <v>-0.2451354046712462</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.488122808597764</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.702859825744534</v>
+        <v>-8.589256885936971</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3466934594749564</v>
+        <v>-0.3012522835519311</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.635648896603408</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.907118001074398</v>
+        <v>-8.793515061266834</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4228835324882594</v>
+        <v>-0.3774423565652341</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.763287841217397</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.940770839582871</v>
+        <v>-8.827167899775308</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4318621134072127</v>
+        <v>-0.3864209374841874</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.863701209134434</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.867301007915422</v>
+        <v>-8.753698068107859</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3871024792468121</v>
+        <v>-0.3416613033237867</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.790231377466986</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.042425425301966</v>
+        <v>-8.928822485494402</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4425970254539129</v>
+        <v>-0.3971558495308871</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.965355794853529</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.276877519316455</v>
+        <v>-9.163274579508892</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5435970279613045</v>
+        <v>-0.4981558520382792</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.965355794853529</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.381252250342902</v>
+        <v>-9.267649310535338</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5920191111458593</v>
+        <v>-0.5465779352228339</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.069730525879975</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.434038405943229</v>
+        <v>-9.320435466135665</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6120177835474339</v>
+        <v>-0.5665766076244081</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.165406012462372</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.560075199311518</v>
+        <v>-9.446472259503954</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6597387722656349</v>
+        <v>-0.6142975963426092</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.14015438965263</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.503003427415587</v>
+        <v>-9.389400487608023</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6329197278208616</v>
+        <v>-0.5874785518978363</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.14015438965263</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.644675269139707</v>
+        <v>-9.531072329332144</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6910636914092514</v>
+        <v>-0.6456225154862261</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.14015438965263</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.595084424714873</v>
+        <v>-9.481481484907309</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6561739434744456</v>
+        <v>-0.6107327675514198</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.090563545227796</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.446166090243016</v>
+        <v>-9.332563150435453</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6096577433323858</v>
+        <v>-0.5642165674093604</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.059313954492623</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.220320937523606</v>
+        <v>-9.106717997716043</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5097406092084129</v>
+        <v>-0.4642994332853876</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.017387278905459</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.095742281186014</v>
+        <v>-8.982139341378451</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4587700021173173</v>
+        <v>-0.413328826194292</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.017387278905459</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.148637569230301</v>
+        <v>-9.035034629422737</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4772943431729244</v>
+        <v>-0.4318531672498991</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.012431932817013</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.07650439394242</v>
+        <v>-8.962901454134856</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4427073688191356</v>
+        <v>-0.3972661928961099</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.012431932817013</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.005138001332773</v>
+        <v>-8.891535061525209</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4238980741691418</v>
+        <v>-0.3784568982461165</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.941065540207365</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.911678967347548</v>
+        <v>-8.798076027539985</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3963979418879595</v>
+        <v>-0.3509567659649342</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.941065540207365</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.64443716647915</v>
+        <v>-8.530834226671587</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2913357820399742</v>
+        <v>-0.2458946061169489</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.941065540207365</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.54653012780266</v>
+        <v>-8.432927187995096</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2524732815428385</v>
+        <v>-0.2070321056198132</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.873079790346809</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.522576586826702</v>
+        <v>-8.408973647019138</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.242223359006962</v>
+        <v>-0.1967821830839367</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.849126249370851</v>
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.258516648503905</v>
+        <v>-8.178522488142235</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1498596998395954</v>
+        <v>-0.1178620356949276</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.585066311048055</v>
+        <v>-1.618675090493948</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.202863597246881</v>
+        <v>2.182698329579345</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.551437024999067</v>
+        <v>-7.471442864637397</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1301851159020391</v>
+        <v>0.1621827800467068</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.585066311048055</v>
+        <v>-1.618675090493948</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.20007656358658</v>
+        <v>2.179911295919045</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.511252726632876</v>
+        <v>-7.431258566271207</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1466024591363566</v>
+        <v>0.1786001232810244</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.544882012681864</v>
+        <v>-1.578490792127758</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.224530766494136</v>
+        <v>2.2043654988266</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.347852855693514</v>
+        <v>-7.267858695331844</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2113292287328585</v>
+        <v>0.2433268928775263</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.381482141742502</v>
+        <v>-1.415090921188395</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.321937510278511</v>
+        <v>2.301772242610975</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.114371633463915</v>
+        <v>-7.034377473102245</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3126461464625505</v>
+        <v>0.3446438106072183</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.148000919512903</v>
+        <v>-1.181609698958797</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.469950672454122</v>
+        <v>2.449785404786586</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.9647052424564</v>
+        <v>-6.88471108209473</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3696204925525972</v>
+        <v>0.401618156697265</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.055097428270367</v>
+        <v>-1.088706207716261</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.522800556886684</v>
+        <v>2.502635289219149</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.832429768825514</v>
+        <v>-6.752435608463844</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4178981687519787</v>
+        <v>0.4498958328966469</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9228219546394807</v>
+        <v>-0.9564307340853739</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.597533327812243</v>
+        <v>2.577368060144708</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.676691436265772</v>
+        <v>-6.596697275904102</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4830085624635121</v>
+        <v>0.5150062266081803</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7670836220797391</v>
+        <v>-0.8006924015256324</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.693791388035725</v>
+        <v>2.673626120368189</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.427691637582191</v>
+        <v>-6.347697477220521</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5955148231606033</v>
+        <v>0.6275124873052715</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7670836220797391</v>
+        <v>-0.8006924015256324</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.706697729259384</v>
+        <v>2.686532461591848</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.533281627355295</v>
+        <v>-6.453287466993626</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4253028976521431</v>
+        <v>0.4573005617968109</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8726736118528435</v>
+        <v>-0.9062823912987368</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.515367805796302</v>
+        <v>2.495202538128767</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.552016529473892</v>
+        <v>-6.472022369112223</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4663532786817903</v>
+        <v>0.4983509428264585</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8782696215129748</v>
+        <v>-0.9118784009588681</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.56055454187731</v>
+        <v>2.540389274209774</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.404076488066293</v>
+        <v>-6.324082327704623</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4056503725566625</v>
+        <v>0.4376480367013307</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.8579487056044173</v>
+        <v>-0.8915574850503105</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.452868168734277</v>
+        <v>2.432702901066741</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.351106965812304</v>
+        <v>-6.271112805450635</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4181241952047801</v>
+        <v>0.4501218593494478</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.8385879627963216</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.475935895833192</v>
+        <v>2.455770628165656</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.307558559041614</v>
+        <v>-6.227564398679944</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4285829458179631</v>
+        <v>0.4605806099626308</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.8385879627963216</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.468975283738099</v>
+        <v>2.448810016070563</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.065410165587756</v>
+        <v>-5.985416005226086</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5399046575806494</v>
+        <v>0.5719023217253172</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.8385879627963216</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.483437638119242</v>
+        <v>2.463272370451706</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.957151028465234</v>
+        <v>-5.877156868103564</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5777404328888531</v>
+        <v>0.6097380970335209</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.8385879627963216</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.477969758578437</v>
+        <v>2.457804490910901</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.833859893648103</v>
+        <v>-5.753865733286434</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6245549808262822</v>
+        <v>0.65655264497095</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.6816880485332979</v>
+        <v>-0.7152968279791911</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.549442533479292</v>
+        <v>2.529277265811757</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.81271069474466</v>
+        <v>-5.73271653438299</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6407156386249846</v>
+        <v>0.6727133027696528</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.6605388496298545</v>
+        <v>-0.6941476290757478</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.569833031058684</v>
+        <v>2.549667763391148</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.568945252761216</v>
+        <v>-5.488951092399546</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7340025237654131</v>
+        <v>0.7660001879100813</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.6605388496298545</v>
+        <v>-0.6941476290757478</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.565613739405734</v>
+        <v>2.545448471738198</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.467182432483921</v>
+        <v>-5.387188272122251</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7768319657963469</v>
+        <v>0.8088296299410151</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.6473197812374258</v>
+        <v>-0.6809285606833191</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.575669494361208</v>
+        <v>2.555504226693671</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.217332038534846</v>
+        <v>-5.137337878173176</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.869514198359679</v>
+        <v>0.9015118625043472</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.6473197812374258</v>
+        <v>-0.6809285606833191</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.56841156934491</v>
+        <v>2.548246301677374</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.041439946067413</v>
+        <v>-4.961445785705743</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9434701588673011</v>
+        <v>0.9754678230119689</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.6473197812374258</v>
+        <v>-0.6809285606833191</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.572010692865558</v>
+        <v>2.551845425198022</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.86999348304495</v>
+        <v>-4.78999932268328</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.02537625013084</v>
+        <v>1.057373914275508</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.4758733182149627</v>
+        <v>-0.5094820976608559</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.68820607673359</v>
+        <v>2.668040809066054</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.795703917306611</v>
+        <v>-4.715709756944941</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.054112554042473</v>
+        <v>1.086110218187141</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4015837524766234</v>
+        <v>-0.4351925319225167</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.731800293792891</v>
+        <v>2.711635026125355</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.732068175072676</v>
+        <v>-4.652074014711006</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.084261651990364</v>
+        <v>1.116259316135032</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3379480102426889</v>
+        <v>-0.3715567896885821</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.774676540187568</v>
+        <v>2.754511272520033</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.620641415746756</v>
+        <v>-4.540647255385086</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.110026614504527</v>
+        <v>1.142024278649195</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3379480102426889</v>
+        <v>-0.3715567896885821</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.755870798971364</v>
+        <v>2.735705531303828</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.380210918941896</v>
+        <v>-4.300216758580226</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.207941889851349</v>
+        <v>1.239939553996017</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.09751751343782861</v>
+        <v>-0.1311262928837219</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.901872173679158</v>
+        <v>2.881706906011622</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367681</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.307968350770701</v>
+        <v>-4.227974190409031</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.240768230954647</v>
+        <v>1.272765895099315</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.09751751343782861</v>
+        <v>-0.1311262928837219</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.905801487513978</v>
+        <v>2.885636219846442</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879963</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.254970028489313</v>
+        <v>-4.174975868127643</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.262646143784542</v>
+        <v>1.29464380792921</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.04218125443588977</v>
+        <v>-0.07579003388178301</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.939681826832481</v>
+        <v>2.919516559164945</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.146165143009586</v>
+        <v>-4.066170982647916</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.303166169196426</v>
+        <v>1.335163833341094</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.04218125443588977</v>
+        <v>-0.07579003388178301</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.936679898052475</v>
+        <v>2.916514630384939</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.926144344972575</v>
+        <v>-3.846150184610905</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.392753525421845</v>
+        <v>1.424751189566513</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.09903859063209047</v>
+        <v>0.06542981118619723</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.022990842103877</v>
+        <v>3.002825574436341</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.793276655909297</v>
+        <v>-3.713282495547627</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.46179478384898</v>
+        <v>1.493792447993648</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.09903859063209047</v>
+        <v>0.06542981118619723</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.0388850249057</v>
+        <v>3.018719757238165</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.673103572544798</v>
+        <v>-3.593109412183129</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.511009861635081</v>
+        <v>1.543007525779749</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.2192116739965894</v>
+        <v>0.1856028945506962</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.112134719364701</v>
+        <v>3.091969451697166</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.528431427445061</v>
+        <v>-3.448437267083391</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.578966822236416</v>
+        <v>1.610964486381084</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3638838190963268</v>
+        <v>0.3302750396504336</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.209026108985984</v>
+        <v>3.188860841318448</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.588306254802753</v>
+        <v>-3.508312094441083</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.541054382694765</v>
+        <v>1.573052046839433</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3040089917386347</v>
+        <v>0.2704002122927415</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.159138703972794</v>
+        <v>3.138973436305259</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.468486023891916</v>
+        <v>-3.388491863530246</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.604271644293308</v>
+        <v>1.636269308437976</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3040089917386347</v>
+        <v>0.2704002122927415</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.174427873207003</v>
+        <v>3.154262605539467</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.470955730353722</v>
+        <v>-3.390961569992052</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.510927961031027</v>
+        <v>1.542925625175695</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.3015392852768286</v>
+        <v>0.2679305058309353</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.080590248652361</v>
+        <v>3.060424980984825</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.539325916677732</v>
+        <v>-3.459331756316062</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.402841747986725</v>
+        <v>1.434839412131393</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.2772062048671503</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.005417529559391</v>
+        <v>2.985252261891855</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.553113969524778</v>
+        <v>-3.473119809163109</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.387763235479798</v>
+        <v>1.419760899624465</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.2772062048671503</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.995854238191282</v>
+        <v>2.975688970523747</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.584107128853484</v>
+        <v>-3.504112968491814</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.200075536788702</v>
+        <v>1.23207320093337</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.2772062048671503</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.820563803231669</v>
+        <v>2.800398535564133</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.408632869061015</v>
+        <v>-3.328638708699345</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.274832472697478</v>
+        <v>1.306830136842146</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.2772062048671503</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.825131035223457</v>
+        <v>2.804965767555921</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.519569121702263</v>
+        <v>-3.439574961340593</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.206200000402185</v>
+        <v>1.238197664546853</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.2772062048671503</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.800873063984664</v>
+        <v>2.780707796317128</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.485905576229981</v>
+        <v>-3.405911415868311</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.222796803811004</v>
+        <v>1.254794467955672</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3444785297853253</v>
+        <v>0.3108697503394321</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.824202576487939</v>
+        <v>2.804037308820403</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.426052957026258</v>
+        <v>-3.346058796664588</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.256910237924625</v>
+        <v>1.288907902069293</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3444785297853253</v>
+        <v>0.3108697503394321</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.834374962920071</v>
+        <v>2.814209695252535</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.339809493999881</v>
+        <v>-3.259815333638211</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.286353893709036</v>
+        <v>1.318351557853704</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3444785297853253</v>
+        <v>0.3108697503394321</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.829321233493931</v>
+        <v>2.809155965826395</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.385116313398861</v>
+        <v>-3.305122153037191</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.26000694139397</v>
+        <v>1.292004605538638</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3036683667760945</v>
+        <v>0.2700595873302013</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.796610911132919</v>
+        <v>2.776445643465383</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.414149418101162</v>
+        <v>-3.334155257739492</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.248945572546151</v>
+        <v>1.280943236690819</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3036683667760945</v>
+        <v>0.2700595873302013</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.79716278416602</v>
+        <v>2.776997516498484</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.321338936650303</v>
+        <v>-3.241344776288633</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.21534245701786</v>
+        <v>1.247340121162528</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3964788482269539</v>
+        <v>0.3628700687810607</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.782121764927902</v>
+        <v>2.761956497260365</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.365728405979731</v>
+        <v>-3.285734245618061</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.19946014521069</v>
+        <v>1.231457809355358</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3520893788975262</v>
+        <v>0.318480599451633</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.757361559254845</v>
+        <v>2.73719629158731</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.25305718774348</v>
+        <v>-3.173063027381811</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.239604341016913</v>
+        <v>1.271602005161581</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4647605971337764</v>
+        <v>0.4311518176878832</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.820039998708319</v>
+        <v>2.799874731040783</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.140680186560808</v>
+        <v>-3.060686026199138</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.290046437320649</v>
+        <v>1.322044101465317</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4647605971337764</v>
+        <v>0.4311518176878832</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.825531294538986</v>
+        <v>2.80536602687145</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.168460584462161</v>
+        <v>-3.088466424100491</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.290431479928647</v>
+        <v>1.322429144073315</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4369801992324234</v>
+        <v>0.4033714197865301</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.820360257566713</v>
+        <v>2.800194989899177</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.25146186548744</v>
+        <v>-3.17146770512577</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.095586687519189</v>
+        <v>1.127584351663857</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4184093147052496</v>
+        <v>0.3848005352593564</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.647573446851062</v>
+        <v>2.627408179183526</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.360075943930771</v>
+        <v>-3.280081783569101</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.172290716861062</v>
+        <v>1.20428838100573</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4184093147052496</v>
+        <v>0.3848005352593564</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.767723107570268</v>
+        <v>2.747557839902732</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.324666905682628</v>
+        <v>-3.244672745320958</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.200967358262642</v>
+        <v>1.23296502240731</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4184093147052496</v>
+        <v>0.3848005352593564</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.782236133672591</v>
+        <v>2.762070866005055</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.286283243124477</v>
+        <v>-3.206289082762807</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.213740264628271</v>
+        <v>1.245737928772939</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4567929772634008</v>
+        <v>0.4231841978175075</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.80268577254985</v>
+        <v>2.782520504882314</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.109166913089311</v>
+        <v>-3.029172752727641</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.28131582548764</v>
+        <v>1.313313489632308</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4567929772634008</v>
+        <v>0.4231841978175075</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.799414801395153</v>
+        <v>2.779249533727616</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.154259157922857</v>
+        <v>-3.074264997561187</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.263962319316135</v>
+        <v>1.295959983460803</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.394896934094011</v>
+        <v>0.3612881546481178</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.762960567255432</v>
+        <v>2.742795299587896</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.029019991416763</v>
+        <v>-2.894889576322419</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.307844961224987</v>
+        <v>1.361497127262724</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4339184020500682</v>
+        <v>0.5180649128188364</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.78016042333548</v>
+        <v>2.830648329796742</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.074034204937369</v>
+        <v>-2.939903789843025</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.270646731148334</v>
+        <v>1.324298897186072</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4035695067354636</v>
+        <v>0.4877160175042318</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.742758541478307</v>
+        <v>2.793246447939568</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.341038715209804</v>
+        <v>-3.206908300115461</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.169536489378306</v>
+        <v>1.223188655416043</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.209206468692515</v>
+        <v>0.2933529794612832</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.631832280991484</v>
+        <v>2.682320187452745</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.442236496646977</v>
+        <v>-3.308106081552634</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.128261298699938</v>
+        <v>1.181913464737675</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1407976551471958</v>
+        <v>0.224944165915964</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.589990914760794</v>
+        <v>2.640478821222055</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.435725530032665</v>
+        <v>-3.301595114938321</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.12846564689998</v>
+        <v>1.182117812937717</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1407976551471958</v>
+        <v>0.224944165915964</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.587590876315111</v>
+        <v>2.638078782776371</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.416687402325367</v>
+        <v>-3.282556987231024</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.132605617191144</v>
+        <v>1.186257783228881</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.08261404381600129</v>
+        <v>0.1667605545847695</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.549205428724639</v>
+        <v>2.5996933351859</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.447814033475985</v>
+        <v>-3.313683618381642</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.297736833669577</v>
+        <v>1.351388999707315</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.08261404381600129</v>
+        <v>0.1667605545847695</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.72678729766332</v>
+        <v>2.77727520412458</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.461680794809903</v>
+        <v>-3.327550379715559</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.293023458122144</v>
+        <v>1.346675624159881</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.04475612708217835</v>
+        <v>0.1289026378509465</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.704905876609159</v>
+        <v>2.75539378307042</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.416876623269973</v>
+        <v>-3.282746208175629</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.316953657135042</v>
+        <v>1.370605823172779</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.04475612708217835</v>
+        <v>0.1289026378509465</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.710914407006085</v>
+        <v>2.761402313467346</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.269133653034971</v>
+        <v>-3.135003237940627</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.274001066506242</v>
+        <v>1.327653232543979</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2125634843170615</v>
+        <v>0.2967099950858297</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.709549042624214</v>
+        <v>2.760036949085475</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.371148335566192</v>
+        <v>-3.237017920471848</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.235988815025234</v>
+        <v>1.289640981062972</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2125634843170615</v>
+        <v>0.2967099950858297</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.712342664155695</v>
+        <v>2.762830570616956</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.364995629513407</v>
+        <v>-3.230865214419063</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.239112245838007</v>
+        <v>1.292764411875744</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2187161903698458</v>
+        <v>0.302862701138614</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.716696636179024</v>
+        <v>2.767184542640285</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.381804927663909</v>
+        <v>-3.247674512569565</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.231469003317916</v>
+        <v>1.285121169355654</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2019068922193442</v>
+        <v>0.2860534029881123</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.705691534028834</v>
+        <v>2.756179440490095</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.319506928887787</v>
+        <v>-3.185376513793443</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.322723756625186</v>
+        <v>1.376375922662923</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2019068922193442</v>
+        <v>0.2860534029881123</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.772027087825655</v>
+        <v>2.822514994286915</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.117716731222629</v>
+        <v>-2.983586316128285</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.205731837405376</v>
+        <v>1.259384003443114</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3999250843884986</v>
+        <v>0.4840715951572667</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.693130004841274</v>
+        <v>2.743617911302535</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.044338634133892</v>
+        <v>-2.910208219039549</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.305373308563046</v>
+        <v>1.359025474600783</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4733031814772351</v>
+        <v>0.5574496922460033</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.807447095416691</v>
+        <v>2.857935001877952</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.142079178758867</v>
+        <v>-3.007948763664523</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.2809048268291</v>
+        <v>1.334556992866837</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4574139033442549</v>
+        <v>0.541560414113023</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.812541264652947</v>
+        <v>2.863029171114208</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.318416938881796</v>
+        <v>-3.184286523787452</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.2089057036046</v>
+        <v>1.262557869642337</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2810761432213255</v>
+        <v>0.3652226539900936</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.705274589403861</v>
+        <v>2.755762495865122</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.241994892449869</v>
+        <v>-3.107864477355526</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.237966140217299</v>
+        <v>1.291618306255037</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2810761432213255</v>
+        <v>0.3652226539900936</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.70376620744379</v>
+        <v>2.75425411390505</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.1976217608113</v>
+        <v>-3.063491345716957</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.255578260308163</v>
+        <v>1.3092304263459</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3254492748598941</v>
+        <v>0.4095957856286622</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.730252953862367</v>
+        <v>2.780740860323628</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.074787539924133</v>
+        <v>-2.940657124829789</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.29910574280162</v>
+        <v>1.352757908839358</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3254492748598941</v>
+        <v>0.4095957856286622</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.724646748000958</v>
+        <v>2.775134654462218</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.027131809363078</v>
+        <v>-2.893001394268734</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.324549792053847</v>
+        <v>1.378201958091585</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3731050054209498</v>
+        <v>0.4572515161897179</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.759621943365395</v>
+        <v>2.810109849826656</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.926613650864323</v>
+        <v>-2.792483235769979</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.369649428828074</v>
+        <v>1.423301594865811</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4736231639197043</v>
+        <v>0.5577696746884724</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.824825211839373</v>
+        <v>2.875313118300634</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.987280241266712</v>
+        <v>-2.853149826172368</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.33213746514299</v>
+        <v>1.385789631180728</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3919248472011707</v>
+        <v>0.4760713579699387</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.762560894284125</v>
+        <v>2.813048800745386</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.942441839658314</v>
+        <v>-2.80831142456397</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.354170528396978</v>
+        <v>1.407822694434716</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3964682801460401</v>
+        <v>0.4806147909148082</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.769384656661675</v>
+        <v>2.819872563122936</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917052</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.043200475415313</v>
+        <v>-2.909070060320969</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.318028013725257</v>
+        <v>1.371680179762994</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3076427114190347</v>
+        <v>0.3917892221878028</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.72025025505655</v>
+        <v>2.770738161517811</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82668474540596</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.998997638329412</v>
+        <v>-2.864867223235068</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.341588751087454</v>
+        <v>1.395240917125191</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.3518455485049352</v>
+        <v>0.4359920592737032</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.752651559835928</v>
+        <v>2.803139466297188</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.035976665992855</v>
+        <v>-2.901846250898512</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.325207140491324</v>
+        <v>1.378859306529062</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.3888194502962657</v>
+        <v>0.4729659610650337</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.773245901379974</v>
+        <v>2.823733807841234</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.877685248453583</v>
+        <v>-2.743554833359239</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.439771472690073</v>
+        <v>1.49342363872781</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.3888194502962657</v>
+        <v>0.4729659610650337</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.824493666563013</v>
+        <v>2.874981573024274</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.670043244819107</v>
+        <v>-2.535912829724763</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.521268978738116</v>
+        <v>1.574921144775854</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.5964614539307418</v>
+        <v>0.6806079646995099</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.947519573337952</v>
+        <v>2.998007479799213</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.619011152096579</v>
+        <v>-2.484880737002235</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.536630044065398</v>
+        <v>1.590282210103135</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.6474935466532697</v>
+        <v>0.7316400574220379</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.973087057209739</v>
+        <v>3.023574963670999</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.553786970969373</v>
+        <v>-2.419656555875029</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.579907120608985</v>
+        <v>1.633559286646722</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.7127177277804754</v>
+        <v>0.7968642385492435</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.029408969978767</v>
+        <v>3.079896876440028</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.516359950898239</v>
+        <v>-2.382229535803896</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.590838900936719</v>
+        <v>1.644491066974456</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.717969265809657</v>
+        <v>0.8021157765784251</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.028520865095556</v>
+        <v>3.079008771556817</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.536471606932948</v>
+        <v>-2.402341191838604</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.584051030854076</v>
+        <v>1.637703196891813</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.7289966108070762</v>
+        <v>0.8131431215758443</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.036394064425248</v>
+        <v>3.086881970886509</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.482726792505743</v>
+        <v>-2.348596377411399</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.766106727646168</v>
+        <v>1.819758893683906</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.7390599202475382</v>
+        <v>0.8232064310163063</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.202989821110736</v>
+        <v>3.253477727571997</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.458935223899601</v>
+        <v>-2.324804808805257</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.895736264306443</v>
+        <v>1.94938843034418</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.7628514888536805</v>
+        <v>0.8469979996224486</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.337377671492239</v>
+        <v>3.387865577953499</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.432851139635793</v>
+        <v>-2.298720724541449</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.897877874025825</v>
+        <v>1.951530040063562</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.7628514888536805</v>
+        <v>0.8469979996224486</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.329085647506098</v>
+        <v>3.379573553967358</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.354719958786846</v>
+        <v>-2.220589543692502</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.927323541949183</v>
+        <v>1.980975707986921</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.837028299737365</v>
+        <v>0.9211748105061331</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.371784929620088</v>
+        <v>3.422272836081349</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.345827497393563</v>
+        <v>-2.211697082299219</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.948434932233288</v>
+        <v>2.002087098271025</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.837028299737365</v>
+        <v>0.9211748105061331</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.389339335346879</v>
+        <v>3.43982724180814</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.514303614363441</v>
+        <v>-2.380173199269097</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.87289953284992</v>
+        <v>1.926551698887658</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.8090804640207843</v>
+        <v>0.8932269747895524</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.364425681321515</v>
+        <v>3.414913587782776</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.816504085501857</v>
+        <v>-1.682373670407514</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.133289041582415</v>
+        <v>2.186941207620153</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.7387324046503736</v>
+        <v>0.8228789154191416</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.30348654288713</v>
+        <v>3.353974449348391</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.793782981818705</v>
+        <v>-1.659652566724361</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.133041505552581</v>
+        <v>2.186693671590318</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.7387324046503736</v>
+        <v>0.8228789154191416</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.294150565384035</v>
+        <v>3.344638471845296</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.792057938528661</v>
+        <v>-1.657927523434317</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.292637648719768</v>
+        <v>2.346289814757505</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7404574479404173</v>
+        <v>0.8246039587091853</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.45409171720923</v>
+        <v>3.504579623670491</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.946838945306916</v>
+        <v>-1.812708530212573</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.267803068502112</v>
+        <v>2.32145523453985</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7070897738859412</v>
+        <v>0.7912362846547092</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.471148935270191</v>
+        <v>3.521636841731452</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.895403611922257</v>
+        <v>-1.761273196827913</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.285052557845521</v>
+        <v>2.338704723883259</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7585251072706009</v>
+        <v>0.8426716180393689</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.498685491290532</v>
+        <v>3.549173397751793</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.868452387595769</v>
+        <v>-1.734321972501425</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.305839201220858</v>
+        <v>2.359491367258595</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.77340545329832</v>
+        <v>0.857551964067088</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.517619852551905</v>
+        <v>3.568107759013166</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.004405395652085</v>
+        <v>-1.870274980557741</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.435561130143291</v>
+        <v>2.489213296181028</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.77340545329832</v>
+        <v>0.857551964067088</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.701722984696865</v>
+        <v>3.752210891158125</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.026813513456957</v>
+        <v>-1.892683098362613</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.418714577924336</v>
+        <v>2.472366743962073</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.77340545329832</v>
+        <v>0.857551964067088</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.693839679599858</v>
+        <v>3.744327586061118</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.174819280936356</v>
+        <v>-2.040688865842013</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.361566270482213</v>
+        <v>2.41521843651995</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6866784444347785</v>
+        <v>0.7708249552035465</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.64385747383137</v>
+        <v>3.694345380292631</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.184260206824886</v>
+        <v>-2.050129791730543</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.414043617848648</v>
+        <v>2.467695783886386</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.80910556197817</v>
+        <v>0.893252072746938</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.773567462079252</v>
+        <v>3.824055368540513</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.18297344328533</v>
+        <v>-2.048843028190986</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.417449417809772</v>
+        <v>2.471101583847509</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8103923255177266</v>
+        <v>0.8945388362864946</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.777230614748287</v>
+        <v>3.827718521209548</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.184530497274621</v>
+        <v>-2.050400082180277</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.414938409107831</v>
+        <v>2.468590575145568</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8103923255177266</v>
+        <v>0.8945388362864946</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.775342427642062</v>
+        <v>3.825830334103323</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.191802382798086</v>
+        <v>-2.057671967703742</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.406849884501307</v>
+        <v>2.460502050539044</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8031204399942617</v>
+        <v>0.8872669507630297</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.765799525930845</v>
+        <v>3.816287432392107</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.189961363739835</v>
+        <v>-2.055830948645491</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.40602030233476</v>
+        <v>2.459672468372497</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8043886666657302</v>
+        <v>0.8885351774344982</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.764994472143879</v>
+        <v>3.81548237860514</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.196870069239515</v>
+        <v>-2.062739654145171</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.416330227000806</v>
+        <v>2.469982393038543</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8043886666657302</v>
+        <v>0.8885351774344982</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.778067879009797</v>
+        <v>3.828555785471059</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763532</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.198431712054375</v>
+        <v>-2.064301296960031</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.415705569874862</v>
+        <v>2.4693577359126</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8043886666657302</v>
+        <v>0.8885351774344982</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.778067879009797</v>
+        <v>3.828555785471059</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.226332499163848</v>
+        <v>-2.092202084069504</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.403069296158075</v>
+        <v>2.456721462195812</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7697917425227954</v>
+        <v>0.8539382532915634</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.755833765651039</v>
+        <v>3.8063216721123</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.229365496676522</v>
+        <v>-2.095235081582178</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.398620541130204</v>
+        <v>2.452272707167942</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7667587450101214</v>
+        <v>0.8509052557788894</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.750778411120633</v>
+        <v>3.801266317581894</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.249426817953029</v>
+        <v>-2.115296402858685</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.457301972210105</v>
+        <v>2.510954138247842</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7466974237336144</v>
+        <v>0.8308439345023824</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.805447577945233</v>
+        <v>3.855935484406493</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.506147635947853</v>
+        <v>-2.372017220853509</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.494925364014023</v>
+        <v>2.54857753005176</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6382828495897995</v>
+        <v>0.7224293603585675</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.880710552460791</v>
+        <v>3.931198458922052</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.660134053723993</v>
+        <v>-2.526003638629649</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.502311066049206</v>
+        <v>2.555963232086944</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6382828495897995</v>
+        <v>0.7224293603585675</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.94969082160643</v>
+        <v>4.000178728067691</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.609612149896327</v>
+        <v>-2.475481734801984</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.508571029700393</v>
+        <v>2.562223195738131</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6382828495897995</v>
+        <v>0.7224293603585675</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.935742023726552</v>
+        <v>3.986229930187812</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.862087303904052</v>
+        <v>-2.727956888809708</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.419451457152717</v>
+        <v>2.473103623190455</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6382828495897995</v>
+        <v>0.7224293603585675</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.947612512781966</v>
+        <v>3.998100419243226</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.13156010582576</v>
+        <v>-2.997429690731416</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.312872870902978</v>
+        <v>2.366525036940716</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6382828495897995</v>
+        <v>0.7224293603585675</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.948823047300909</v>
+        <v>3.99931095376217</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
         <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.289104177555201</v>
+        <v>-3.284239526758868</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.253976984438523</v>
+        <v>2.255922844757056</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5713810444495251</v>
+        <v>0.5883251059267368</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.912803706444066</v>
+        <v>3.922970143330393</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.818754475057874</v>
+        <v>3.795124507020073</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.567724630067084</v>
+        <v>3.56505293251054</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.289104177555201</v>
+        <v>-3.39853977670929</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.253976984438523</v>
+        <v>2.205280597513077</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5713810444495251</v>
+        <v>0.5220329132726447</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.560788427053451</v>
+        <v>3.878272680474127</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240711.xlsx
+++ b/tame_output/ON/bt/strategyON_20240711.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.1%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-50.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.9%</t>
+          <t>-67.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.7%</t>
+          <t>457.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-501.4%</t>
+          <t>-504.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-156.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-125.0%</t>
+          <t>-128.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-171.8%</t>
+          <t>-147.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-43.6%</t>
         </is>
       </c>
     </row>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.626873253827722</v>
+        <v>-6.789867050568925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4677729678478526</v>
+        <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.722400026520157</v>
+        <v>-6.995118069805685</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4256618239165735</v>
+        <v>0.3165746066023623</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.885979904704541</v>
+        <v>-7.158697947990069</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3586347926978211</v>
+        <v>0.2495475753836098</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.182641246514739</v>
+        <v>-7.455359289800266</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2437492319029499</v>
+        <v>0.1346620145887392</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.369360954824042</v>
+        <v>-7.642078998109569</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1650350440448261</v>
+        <v>0.05594782673061482</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.752362343566673</v>
+        <v>-8.025080386852199</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.01173238722618919</v>
+        <v>-0.09735483008802115</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.934232134551708</v>
+        <v>-8.206950177837234</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05844401319639481</v>
+        <v>-0.1675312305106051</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.340154467722146</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.29376245705571</v>
+        <v>-8.566480500341235</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1969058388999452</v>
+        <v>-0.3059930562141555</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.340154467722146</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.344111520509932</v>
+        <v>-8.616829563795458</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2091294443244567</v>
+        <v>-0.3182166616386666</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.390503531176368</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.441730797931328</v>
+        <v>-8.714448841216853</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2451354046712462</v>
+        <v>-0.3542226219854565</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.488122808597764</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.589256885936971</v>
+        <v>-8.861974929222496</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3012522835519311</v>
+        <v>-0.4103395008661415</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.635648896603408</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.793515061266834</v>
+        <v>-9.06623310455236</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3774423565652341</v>
+        <v>-0.4865295738794444</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.763287841217397</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.827167899775308</v>
+        <v>-9.099885943060833</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3864209374841874</v>
+        <v>-0.4955081547983977</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.863701209134434</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.753698068107859</v>
+        <v>-9.026416111393385</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3416613033237867</v>
+        <v>-0.4507485206379971</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.790231377466986</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.928822485494402</v>
+        <v>-9.201540528779928</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3971558495308871</v>
+        <v>-0.5062430668450975</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.965355794853529</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.163274579508892</v>
+        <v>-9.435992622794418</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4981558520382792</v>
+        <v>-0.6072430693524895</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.965355794853529</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.267649310535338</v>
+        <v>-9.540367353820864</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5465779352228339</v>
+        <v>-0.6556651525370443</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.069730525879975</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.320435466135665</v>
+        <v>-9.593153509421191</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5665766076244081</v>
+        <v>-0.6756638249386184</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.165406012462372</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.446472259503954</v>
+        <v>-9.71919030278948</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6142975963426092</v>
+        <v>-0.7233848136568195</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.14015438965263</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.389400487608023</v>
+        <v>-9.662118530893549</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5874785518978363</v>
+        <v>-0.6965657692120466</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.14015438965263</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.531072329332144</v>
+        <v>-9.803790372617669</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6456225154862261</v>
+        <v>-0.7547097328004364</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.14015438965263</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.481481484907309</v>
+        <v>-9.754199528192835</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6107327675514198</v>
+        <v>-0.7198199848656301</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.090563545227796</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.332563150435453</v>
+        <v>-9.605281193720979</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5642165674093604</v>
+        <v>-0.6733037847235708</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.059313954492623</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.106717997716043</v>
+        <v>-9.379436041001568</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4642994332853876</v>
+        <v>-0.5733866505995979</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.017387278905459</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.982139341378451</v>
+        <v>-9.254857384663977</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.413328826194292</v>
+        <v>-0.5224160435085023</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.017387278905459</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.035034629422737</v>
+        <v>-9.307752672708263</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4318531672498991</v>
+        <v>-0.5409403845641094</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.012431932817013</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.962901454134856</v>
+        <v>-9.235619497420382</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3972661928961099</v>
+        <v>-0.5063534102103202</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.012431932817013</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.891535061525209</v>
+        <v>-9.164253104810735</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3784568982461165</v>
+        <v>-0.4875441155603264</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.941065540207365</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.798076027539985</v>
+        <v>-9.07079407082551</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3509567659649342</v>
+        <v>-0.4600439832791445</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.941065540207365</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.530834226671587</v>
+        <v>-8.803552269957112</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2458946061169489</v>
+        <v>-0.3549818234311588</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.941065540207365</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.432927187995096</v>
+        <v>-8.705645231280622</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2070321056198132</v>
+        <v>-0.3161193229340236</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.873079790346809</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.408973647019138</v>
+        <v>-8.681691690304664</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1967821830839367</v>
+        <v>-0.3058694003981466</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.849126249370851</v>
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.178522488142235</v>
+        <v>-8.417631751981867</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1178620356949276</v>
+        <v>-0.2135057412307804</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.618675090493948</v>
+        <v>-1.585066311048055</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.182698329579345</v>
+        <v>2.202863597246881</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.471442864637397</v>
+        <v>-7.710552128477029</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1621827800467068</v>
+        <v>0.06653907451085406</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.618675090493948</v>
+        <v>-1.585066311048055</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.179911295919045</v>
+        <v>2.20007656358658</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.431258566271207</v>
+        <v>-7.670367830110838</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1786001232810244</v>
+        <v>0.0829564177451716</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.578490792127758</v>
+        <v>-1.544882012681864</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.2043654988266</v>
+        <v>2.224530766494136</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.267858695331844</v>
+        <v>-7.506967959171476</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2433268928775263</v>
+        <v>0.1476831873416735</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.415090921188395</v>
+        <v>-1.381482141742502</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.301772242610975</v>
+        <v>2.321937510278511</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.034377473102245</v>
+        <v>-7.273486736941877</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3446438106072183</v>
+        <v>0.2490001050713655</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.181609698958797</v>
+        <v>-1.148000919512903</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.449785404786586</v>
+        <v>2.469950672454122</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.88471108209473</v>
+        <v>-7.123820345934362</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.401618156697265</v>
+        <v>0.3059744511614122</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.088706207716261</v>
+        <v>-1.055097428270367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.502635289219149</v>
+        <v>2.522800556886684</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.752435608463844</v>
+        <v>-6.991544872303476</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4498958328966469</v>
+        <v>0.3542521273607941</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9564307340853739</v>
+        <v>-0.9228219546394807</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.577368060144708</v>
+        <v>2.597533327812243</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.596697275904102</v>
+        <v>-6.835806539743734</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5150062266081803</v>
+        <v>0.4193625210723275</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.8006924015256324</v>
+        <v>-0.7670836220797391</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.673626120368189</v>
+        <v>2.693791388035725</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.347697477220521</v>
+        <v>-6.586806741060153</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6275124873052715</v>
+        <v>0.5318687817694188</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.8006924015256324</v>
+        <v>-0.7670836220797391</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.686532461591848</v>
+        <v>2.706697729259384</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.453287466993626</v>
+        <v>-6.692396730833257</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4573005617968109</v>
+        <v>0.3616568562609581</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.9062823912987368</v>
+        <v>-0.8726736118528435</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.495202538128767</v>
+        <v>2.515367805796302</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.472022369112223</v>
+        <v>-6.711131632951854</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4983509428264585</v>
+        <v>0.4027072372906058</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.9118784009588681</v>
+        <v>-0.8782696215129748</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.540389274209774</v>
+        <v>2.56055454187731</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.324082327704623</v>
+        <v>-6.563191591544255</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4376480367013307</v>
+        <v>0.3420043311654779</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.8915574850503105</v>
+        <v>-0.8579487056044173</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.432702901066741</v>
+        <v>2.452868168734277</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.271112805450635</v>
+        <v>-6.510222069290267</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4501218593494478</v>
+        <v>0.354478153813595</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8385879627963216</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.455770628165656</v>
+        <v>2.475935895833192</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.227564398679944</v>
+        <v>-6.466673662519576</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4605806099626308</v>
+        <v>0.3649369044267781</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8385879627963216</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.448810016070563</v>
+        <v>2.468975283738099</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.985416005226086</v>
+        <v>-6.224525269065718</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5719023217253172</v>
+        <v>0.4762586161894644</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8385879627963216</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.463272370451706</v>
+        <v>2.483437638119242</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.877156868103564</v>
+        <v>-6.116266131943196</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6097380970335209</v>
+        <v>0.5140943914976681</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8385879627963216</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.457804490910901</v>
+        <v>2.477969758578437</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.753865733286434</v>
+        <v>-5.992974997126066</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.65655264497095</v>
+        <v>0.5609089394350972</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.7152968279791911</v>
+        <v>-0.6816880485332979</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.529277265811757</v>
+        <v>2.549442533479292</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.73271653438299</v>
+        <v>-5.971825798222622</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6727133027696528</v>
+        <v>0.5770695972338</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.6941476290757478</v>
+        <v>-0.6605388496298545</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.549667763391148</v>
+        <v>2.569833031058684</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.488951092399546</v>
+        <v>-5.728060356239178</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7660001879100813</v>
+        <v>0.6703564823742285</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.6941476290757478</v>
+        <v>-0.6605388496298545</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.545448471738198</v>
+        <v>2.565613739405734</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.387188272122251</v>
+        <v>-5.626297535961883</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8088296299410151</v>
+        <v>0.7131859244051624</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.6809285606833191</v>
+        <v>-0.6473197812374258</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.555504226693671</v>
+        <v>2.575669494361208</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.137337878173176</v>
+        <v>-5.376447142012808</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9015118625043472</v>
+        <v>0.8058681569684945</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.6809285606833191</v>
+        <v>-0.6473197812374258</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.548246301677374</v>
+        <v>2.56841156934491</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.961445785705743</v>
+        <v>-5.200555049545375</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9754678230119689</v>
+        <v>0.8798241174761161</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.6809285606833191</v>
+        <v>-0.6473197812374258</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.551845425198022</v>
+        <v>2.572010692865558</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.78999932268328</v>
+        <v>-5.029108586522912</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.057373914275508</v>
+        <v>0.9617302087396551</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.5094820976608559</v>
+        <v>-0.4758733182149627</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.668040809066054</v>
+        <v>2.68820607673359</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.715709756944941</v>
+        <v>-4.954819020784573</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.086110218187141</v>
+        <v>0.9904665126512879</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4351925319225167</v>
+        <v>-0.4015837524766234</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.711635026125355</v>
+        <v>2.731800293792891</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.652074014711006</v>
+        <v>-4.891183278550638</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.116259316135032</v>
+        <v>1.020615610599179</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3715567896885821</v>
+        <v>-0.3379480102426889</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.754511272520033</v>
+        <v>2.774676540187568</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.540647255385086</v>
+        <v>-4.779756519224718</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.142024278649195</v>
+        <v>1.046380573113343</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3715567896885821</v>
+        <v>-0.3379480102426889</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.735705531303828</v>
+        <v>2.755870798971364</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.300216758580226</v>
+        <v>-4.539326022419858</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.239939553996017</v>
+        <v>1.144295848460164</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1311262928837219</v>
+        <v>-0.09751751343782861</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.881706906011622</v>
+        <v>2.901872173679158</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.227974190409031</v>
+        <v>-4.467083454248663</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.272765895099315</v>
+        <v>1.177122189563462</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1311262928837219</v>
+        <v>-0.09751751343782861</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.885636219846442</v>
+        <v>2.905801487513978</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.174975868127643</v>
+        <v>-4.25317810812121</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.29464380792921</v>
+        <v>1.263362911931784</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.07579003388178301</v>
+        <v>0.03339705300224366</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.919516559164945</v>
+        <v>2.985028811295361</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.066170982647916</v>
+        <v>-4.144373222641483</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.335163833341094</v>
+        <v>1.303882937343668</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.07579003388178301</v>
+        <v>0.03339705300224366</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.916514630384939</v>
+        <v>2.982026882515355</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.846150184610905</v>
+        <v>-3.924352424604472</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.424751189566513</v>
+        <v>1.393470293569086</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.06542981118619723</v>
+        <v>0.1746168980702239</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.002825574436341</v>
+        <v>3.068337826566757</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.713282495547627</v>
+        <v>-3.791484735541194</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.493792447993648</v>
+        <v>1.462511551996221</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.06542981118619723</v>
+        <v>0.1746168980702239</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.018719757238165</v>
+        <v>3.08423200936858</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.593109412183129</v>
+        <v>-3.671311652176695</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.543007525779749</v>
+        <v>1.511726629782322</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.1856028945506962</v>
+        <v>0.2947899814347228</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.091969451697166</v>
+        <v>3.157481703827582</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.448437267083391</v>
+        <v>-3.526639507076958</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.610964486381084</v>
+        <v>1.579683590383657</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3302750396504336</v>
+        <v>0.4394621265344603</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.188860841318448</v>
+        <v>3.254373093448864</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.508312094441083</v>
+        <v>-3.58651433443465</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.573052046839433</v>
+        <v>1.541771150842006</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.2704002122927415</v>
+        <v>0.3795872991767681</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.138973436305259</v>
+        <v>3.204485688435674</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.388491863530246</v>
+        <v>-3.466694103523813</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.636269308437976</v>
+        <v>1.60498841244055</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.2704002122927415</v>
+        <v>0.3795872991767681</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.154262605539467</v>
+        <v>3.219774857669883</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.390961569992052</v>
+        <v>-3.469163809985619</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.542925625175695</v>
+        <v>1.511644729178269</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.2679305058309353</v>
+        <v>0.377117592714962</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.060424980984825</v>
+        <v>3.125937233115241</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.459331756316062</v>
+        <v>-3.537533996309628</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.434839412131393</v>
+        <v>1.403558516133966</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2772062048671503</v>
+        <v>0.3863932917511769</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.985252261891855</v>
+        <v>3.050764514022271</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.473119809163109</v>
+        <v>-3.551322049156675</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.419760899624465</v>
+        <v>1.388480003627039</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2772062048671503</v>
+        <v>0.3863932917511769</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.975688970523747</v>
+        <v>3.041201222654163</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.504112968491814</v>
+        <v>-3.58231520848538</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.23207320093337</v>
+        <v>1.200792304935943</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.2772062048671503</v>
+        <v>0.3863932917511769</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.800398535564133</v>
+        <v>2.865910787694549</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.328638708699345</v>
+        <v>-3.406840948692911</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.306830136842146</v>
+        <v>1.275549240844719</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.2772062048671503</v>
+        <v>0.3863932917511769</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.804965767555921</v>
+        <v>2.870478019686337</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.439574961340593</v>
+        <v>-3.51777720133416</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.238197664546853</v>
+        <v>1.206916768549427</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.2772062048671503</v>
+        <v>0.3863932917511769</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.780707796317128</v>
+        <v>2.846220048447544</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.405911415868311</v>
+        <v>-3.484113655861878</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.254794467955672</v>
+        <v>1.223513571958245</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3108697503394321</v>
+        <v>0.4200568372234588</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.804037308820403</v>
+        <v>2.869549560950819</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.346058796664588</v>
+        <v>-3.424261036658155</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.288907902069293</v>
+        <v>1.257627006071866</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3108697503394321</v>
+        <v>0.4200568372234588</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.814209695252535</v>
+        <v>2.879721947382951</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.259815333638211</v>
+        <v>-3.338017573631777</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.318351557853704</v>
+        <v>1.287070661856278</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3108697503394321</v>
+        <v>0.4200568372234588</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.809155965826395</v>
+        <v>2.874668217956811</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.305122153037191</v>
+        <v>-3.383324393030757</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.292004605538638</v>
+        <v>1.260723709541211</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.2700595873302013</v>
+        <v>0.379246674214228</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.776445643465383</v>
+        <v>2.841957895595799</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.334155257739492</v>
+        <v>-3.412357497733059</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.280943236690819</v>
+        <v>1.249662340693392</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.2700595873302013</v>
+        <v>0.379246674214228</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.776997516498484</v>
+        <v>2.8425097686289</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.241344776288633</v>
+        <v>-3.3195470162822</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.247340121162528</v>
+        <v>1.216059225165102</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3628700687810607</v>
+        <v>0.4720571556650873</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.761956497260365</v>
+        <v>2.827468749390782</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.285734245618061</v>
+        <v>-3.363936485611627</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.231457809355358</v>
+        <v>1.200176913357931</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.318480599451633</v>
+        <v>0.4276676863356597</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.73719629158731</v>
+        <v>2.802708543717725</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.173063027381811</v>
+        <v>-3.251265267375377</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.271602005161581</v>
+        <v>1.240321109164154</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4311518176878832</v>
+        <v>0.5403389045719098</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.799874731040783</v>
+        <v>2.865386983171199</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.060686026199138</v>
+        <v>-3.138888266192704</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.322044101465317</v>
+        <v>1.290763205467891</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4311518176878832</v>
+        <v>0.5403389045719098</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.80536602687145</v>
+        <v>2.870878279001866</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.088466424100491</v>
+        <v>-3.166668664094058</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.322429144073315</v>
+        <v>1.291148248075888</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4033714197865301</v>
+        <v>0.5125585066705567</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.800194989899177</v>
+        <v>2.865707242029593</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.17146770512577</v>
+        <v>-3.249669945119336</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.127584351663857</v>
+        <v>1.09630345566643</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3848005352593564</v>
+        <v>0.493987622143383</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.627408179183526</v>
+        <v>2.692920431313942</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.280081783569101</v>
+        <v>-3.358284023562668</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.20428838100573</v>
+        <v>1.173007485008303</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3848005352593564</v>
+        <v>0.493987622143383</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.747557839902732</v>
+        <v>2.813070092033148</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.244672745320958</v>
+        <v>-3.322874985314525</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.23296502240731</v>
+        <v>1.201684126409884</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3848005352593564</v>
+        <v>0.493987622143383</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.762070866005055</v>
+        <v>2.827583118135471</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.206289082762807</v>
+        <v>-3.284491322756374</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.245737928772939</v>
+        <v>1.214457032775513</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4231841978175075</v>
+        <v>0.5323712847015342</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.782520504882314</v>
+        <v>2.84803275701273</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.029172752727641</v>
+        <v>-3.107374992721208</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.313313489632308</v>
+        <v>1.282032593634882</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4231841978175075</v>
+        <v>0.5323712847015342</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.779249533727616</v>
+        <v>2.844761785858033</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.074264997561187</v>
+        <v>-3.152467237554753</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.295959983460803</v>
+        <v>1.264679087463376</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3612881546481178</v>
+        <v>0.4704752415321444</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.742795299587896</v>
+        <v>2.808307551718312</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.894889576322419</v>
+        <v>-2.973091816315986</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.361497127262724</v>
+        <v>1.330216231265298</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5180649128188364</v>
+        <v>0.6272519997028631</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.830648329796742</v>
+        <v>2.896160581927157</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.939903789843025</v>
+        <v>-3.018106029836592</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.324298897186072</v>
+        <v>1.293018001188645</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4877160175042318</v>
+        <v>0.5969031043882584</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.793246447939568</v>
+        <v>2.858758700069984</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.206908300115461</v>
+        <v>-3.285110540109027</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.223188655416043</v>
+        <v>1.191907759418616</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2933529794612832</v>
+        <v>0.4025400663453099</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.682320187452745</v>
+        <v>2.747832439583161</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.308106081552634</v>
+        <v>-3.3863083215462</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.181913464737675</v>
+        <v>1.150632568740249</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.224944165915964</v>
+        <v>0.3341312527999907</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.640478821222055</v>
+        <v>2.705991073352471</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.301595114938321</v>
+        <v>-3.379797354931887</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.182117812937717</v>
+        <v>1.150836916940291</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.224944165915964</v>
+        <v>0.3341312527999907</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.638078782776371</v>
+        <v>2.703591034906788</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.282556987231024</v>
+        <v>-3.36075922722459</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.186257783228881</v>
+        <v>1.154976887231455</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1667605545847695</v>
+        <v>0.2759476414687961</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.5996933351859</v>
+        <v>2.665205587316316</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.313683618381642</v>
+        <v>-3.391885858375208</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.351388999707315</v>
+        <v>1.320108103709888</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1667605545847695</v>
+        <v>0.2759476414687961</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.77727520412458</v>
+        <v>2.842787456254996</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.327550379715559</v>
+        <v>-3.405752619709125</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.346675624159881</v>
+        <v>1.315394728162455</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1289026378509465</v>
+        <v>0.2380897247349732</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.75539378307042</v>
+        <v>2.820906035200836</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.282746208175629</v>
+        <v>-3.360948448169196</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.370605823172779</v>
+        <v>1.339324927175352</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1289026378509465</v>
+        <v>0.2380897247349732</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.761402313467346</v>
+        <v>2.826914565597762</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.135003237940627</v>
+        <v>-3.213205477934193</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.327653232543979</v>
+        <v>1.296372336546553</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2967099950858297</v>
+        <v>0.4058970819698564</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.760036949085475</v>
+        <v>2.825549201215892</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.237017920471848</v>
+        <v>-3.315220160465414</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.289640981062972</v>
+        <v>1.258360085065545</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2967099950858297</v>
+        <v>0.4058970819698564</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.762830570616956</v>
+        <v>2.828342822747373</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.230865214419063</v>
+        <v>-3.30906745441263</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.292764411875744</v>
+        <v>1.261483515878318</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.302862701138614</v>
+        <v>0.4120497880226406</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.767184542640285</v>
+        <v>2.832696794770701</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.247674512569565</v>
+        <v>-3.325876752563131</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.285121169355654</v>
+        <v>1.253840273358227</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2860534029881123</v>
+        <v>0.395240489872139</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.756179440490095</v>
+        <v>2.821691692620511</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.185376513793443</v>
+        <v>-3.26357875378701</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.376375922662923</v>
+        <v>1.345095026665497</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2860534029881123</v>
+        <v>0.395240489872139</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.822514994286915</v>
+        <v>2.888027246417332</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.983586316128285</v>
+        <v>-3.061788556121852</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.259384003443114</v>
+        <v>1.228103107445687</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4840715951572667</v>
+        <v>0.5932586820412934</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.743617911302535</v>
+        <v>2.809130163432951</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.910208219039549</v>
+        <v>-2.988410459033115</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.359025474600783</v>
+        <v>1.327744578603357</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5574496922460033</v>
+        <v>0.6666367791300299</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.857935001877952</v>
+        <v>2.923447254008368</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.007948763664523</v>
+        <v>-3.086151003658089</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.334556992866837</v>
+        <v>1.303276096869411</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.541560414113023</v>
+        <v>0.6507475009970498</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.863029171114208</v>
+        <v>2.928541423244624</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.184286523787452</v>
+        <v>-3.262488763781019</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.262557869642337</v>
+        <v>1.231276973644911</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3652226539900936</v>
+        <v>0.4744097408741204</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.755762495865122</v>
+        <v>2.821274747995538</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.107864477355526</v>
+        <v>-3.186066717349092</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.291618306255037</v>
+        <v>1.26033741025761</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3652226539900936</v>
+        <v>0.4744097408741204</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.75425411390505</v>
+        <v>2.819766366035466</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.063491345716957</v>
+        <v>-3.141693585710523</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.3092304263459</v>
+        <v>1.277949530348474</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4095957856286622</v>
+        <v>0.5187828725126891</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.780740860323628</v>
+        <v>2.846253112454044</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.940657124829789</v>
+        <v>-3.018859364823356</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.352757908839358</v>
+        <v>1.321477012841931</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4095957856286622</v>
+        <v>0.5187828725126891</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.775134654462218</v>
+        <v>2.840646906592634</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.893001394268734</v>
+        <v>-2.9712036342623</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.378201958091585</v>
+        <v>1.346921062094158</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4572515161897179</v>
+        <v>0.5664386030737447</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.810109849826656</v>
+        <v>2.875622101957072</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.792483235769979</v>
+        <v>-2.870685475763546</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.423301594865811</v>
+        <v>1.392020698868385</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5577696746884724</v>
+        <v>0.6669567615724993</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.875313118300634</v>
+        <v>2.94082537043105</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.853149826172368</v>
+        <v>-2.931352066165935</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.385789631180728</v>
+        <v>1.354508735183301</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4760713579699387</v>
+        <v>0.5852584448539656</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.813048800745386</v>
+        <v>2.878561052875802</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.80831142456397</v>
+        <v>-2.886513664557537</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.407822694434716</v>
+        <v>1.376541798437289</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4806147909148082</v>
+        <v>0.5898018777988351</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.819872563122936</v>
+        <v>2.885384815253352</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.909070060320969</v>
+        <v>-2.987272300314535</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.371680179762994</v>
+        <v>1.340399283765568</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3917892221878028</v>
+        <v>0.5009763090718297</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.770738161517811</v>
+        <v>2.836250413648227</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.864867223235068</v>
+        <v>-2.943069463228635</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.395240917125191</v>
+        <v>1.363960021127765</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4359920592737032</v>
+        <v>0.5451791461577301</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.803139466297188</v>
+        <v>2.868651718427604</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.901846250898512</v>
+        <v>-2.980048490892078</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.378859306529062</v>
+        <v>1.347578410531635</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4729659610650337</v>
+        <v>0.5821530479490606</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.823733807841234</v>
+        <v>2.88924605997165</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.743554833359239</v>
+        <v>-2.821757073352806</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.49342363872781</v>
+        <v>1.462142742730384</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4729659610650337</v>
+        <v>0.5821530479490606</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.874981573024274</v>
+        <v>2.94049382515469</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.535912829724763</v>
+        <v>-2.61411506971833</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.574921144775854</v>
+        <v>1.543640248778427</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6806079646995099</v>
+        <v>0.7897950515835368</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.998007479799213</v>
+        <v>3.063519731929629</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.484880737002235</v>
+        <v>-2.563082976995802</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.590282210103135</v>
+        <v>1.559001314105709</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7316400574220379</v>
+        <v>0.8408271443060648</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.023574963670999</v>
+        <v>3.089087215801416</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.419656555875029</v>
+        <v>-2.497858795868596</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.633559286646722</v>
+        <v>1.602278390649296</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.7968642385492435</v>
+        <v>0.9060513254332704</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.079896876440028</v>
+        <v>3.145409128570444</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.382229535803896</v>
+        <v>-2.460431775797462</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.644491066974456</v>
+        <v>1.61321017097703</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8021157765784251</v>
+        <v>0.911302863462452</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.079008771556817</v>
+        <v>3.144521023687233</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.402341191838604</v>
+        <v>-2.48054343183217</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.637703196891813</v>
+        <v>1.606422300894387</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8131431215758443</v>
+        <v>0.9223302084598712</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.086881970886509</v>
+        <v>3.152394223016925</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.348596377411399</v>
+        <v>-2.426798617404966</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.819758893683906</v>
+        <v>1.788477997686479</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8232064310163063</v>
+        <v>0.9323935179003332</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.253477727571997</v>
+        <v>3.318989979702413</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.324804808805257</v>
+        <v>-2.403007048798823</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.94938843034418</v>
+        <v>1.918107534346754</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.8469979996224486</v>
+        <v>0.9561850865064755</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.387865577953499</v>
+        <v>3.453377830083916</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.298720724541449</v>
+        <v>-2.376922964535015</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.951530040063562</v>
+        <v>1.920249144066136</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.8469979996224486</v>
+        <v>0.9561850865064755</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.379573553967358</v>
+        <v>3.445085806097774</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.220589543692502</v>
+        <v>-2.298791783686069</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.980975707986921</v>
+        <v>1.949694811989494</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9211748105061331</v>
+        <v>1.03036189739016</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.422272836081349</v>
+        <v>3.487785088211765</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.211697082299219</v>
+        <v>-2.289899322292785</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.002087098271025</v>
+        <v>1.970806202273598</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9211748105061331</v>
+        <v>1.03036189739016</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.43982724180814</v>
+        <v>3.505339493938556</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.380173199269097</v>
+        <v>-2.458375439262663</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.926551698887658</v>
+        <v>1.895270802890231</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.8932269747895524</v>
+        <v>1.002414061673579</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.414913587782776</v>
+        <v>3.480425839913192</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.682373670407514</v>
+        <v>-1.76057591040108</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.186941207620153</v>
+        <v>2.155660311622726</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8228789154191416</v>
+        <v>0.9320660023031686</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.353974449348391</v>
+        <v>3.419486701478807</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.659652566724361</v>
+        <v>-1.737854806717928</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.186693671590318</v>
+        <v>2.155412775592892</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8228789154191416</v>
+        <v>0.9320660023031686</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.344638471845296</v>
+        <v>3.410150723975712</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.657927523434317</v>
+        <v>-1.736129763427884</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.346289814757505</v>
+        <v>2.315008918760078</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8246039587091853</v>
+        <v>0.9337910455932124</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.504579623670491</v>
+        <v>3.570091875800907</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.812708530212573</v>
+        <v>-1.890910770206139</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.32145523453985</v>
+        <v>2.290174338542423</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7912362846547092</v>
+        <v>0.9004233715387362</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.521636841731452</v>
+        <v>3.587149093861868</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.761273196827913</v>
+        <v>-1.83947543682148</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.338704723883259</v>
+        <v>2.307423827885832</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8426716180393689</v>
+        <v>0.9518587049233959</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.549173397751793</v>
+        <v>3.614685649882209</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.734321972501425</v>
+        <v>-1.812524212494992</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.359491367258595</v>
+        <v>2.328210471261169</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.857551964067088</v>
+        <v>0.966739050951115</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.568107759013166</v>
+        <v>3.633620011143582</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.870274980557741</v>
+        <v>-1.948477220551308</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.489213296181028</v>
+        <v>2.457932400183602</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.857551964067088</v>
+        <v>0.966739050951115</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.752210891158125</v>
+        <v>3.817723143288541</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.892683098362613</v>
+        <v>-1.97088533835618</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.472366743962073</v>
+        <v>2.441085847964646</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.857551964067088</v>
+        <v>0.966739050951115</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.744327586061118</v>
+        <v>3.809839838191535</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.040688865842013</v>
+        <v>-2.118891105835579</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.41521843651995</v>
+        <v>2.383937540522524</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7708249552035465</v>
+        <v>0.8800120420875736</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.694345380292631</v>
+        <v>3.759857632423047</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.050129791730543</v>
+        <v>-2.128332031724109</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.467695783886386</v>
+        <v>2.436414887888959</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.893252072746938</v>
+        <v>1.002439159630965</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.824055368540513</v>
+        <v>3.889567620670929</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.048843028190986</v>
+        <v>-2.127045268184553</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.471101583847509</v>
+        <v>2.439820687850083</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8945388362864946</v>
+        <v>1.003725923170522</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.827718521209548</v>
+        <v>3.893230773339964</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.050400082180277</v>
+        <v>-2.128602322173844</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.468590575145568</v>
+        <v>2.437309679148141</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8945388362864946</v>
+        <v>1.003725923170522</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.825830334103323</v>
+        <v>3.891342586233739</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.057671967703742</v>
+        <v>-2.135874207697309</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.460502050539044</v>
+        <v>2.429221154541618</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8872669507630297</v>
+        <v>0.9964540376470568</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.816287432392107</v>
+        <v>3.881799684522523</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.055830948645491</v>
+        <v>-2.134033188639057</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.459672468372497</v>
+        <v>2.42839157237507</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8885351774344982</v>
+        <v>0.9977222643185253</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.81548237860514</v>
+        <v>3.880994630735556</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647107</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.062739654145171</v>
+        <v>-2.140941894138738</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.469982393038543</v>
+        <v>2.438701497041117</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8885351774344982</v>
+        <v>0.9977222643185253</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.828555785471059</v>
+        <v>3.894068037601475</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.064301296960031</v>
+        <v>-2.142503536953598</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.4693577359126</v>
+        <v>2.438076839915173</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8885351774344982</v>
+        <v>0.9977222643185253</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.828555785471059</v>
+        <v>3.894068037601475</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.092202084069504</v>
+        <v>-2.170404324063071</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.456721462195812</v>
+        <v>2.425440566198386</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8539382532915634</v>
+        <v>0.9631253401755905</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.8063216721123</v>
+        <v>3.871833924242716</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.095235081582178</v>
+        <v>-2.173437321575745</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.452272707167942</v>
+        <v>2.420991811170515</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8509052557788894</v>
+        <v>0.9600923426629167</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.801266317581894</v>
+        <v>3.86677856971231</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971081</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.115296402858685</v>
+        <v>-2.193498642852251</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.510954138247842</v>
+        <v>2.479673242250416</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8308439345023824</v>
+        <v>0.9400310213864096</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.855935484406493</v>
+        <v>3.921447736536909</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199807</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.372017220853509</v>
+        <v>-2.450219460847075</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.54857753005176</v>
+        <v>2.517296634054333</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.7224293603585675</v>
+        <v>0.8316164472425948</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.931198458922052</v>
+        <v>3.996710711052468</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622238</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.526003638629649</v>
+        <v>-2.604205878623216</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.555963232086944</v>
+        <v>2.524682336089517</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.7224293603585675</v>
+        <v>0.8316164472425948</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.000178728067691</v>
+        <v>4.065690980198108</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808531</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.475481734801984</v>
+        <v>-2.55368397479555</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.562223195738131</v>
+        <v>2.530942299740704</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.7224293603585675</v>
+        <v>0.8316164472425948</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.986229930187812</v>
+        <v>4.051742182318229</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994896</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.727956888809708</v>
+        <v>-2.806159128803275</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.473103623190455</v>
+        <v>2.441822727193029</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.7224293603585675</v>
+        <v>0.8316164472425948</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.998100419243226</v>
+        <v>4.063612671373643</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.997429690731416</v>
+        <v>-3.075631930724983</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.366525036940716</v>
+        <v>2.335244140943288</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.7224293603585675</v>
+        <v>0.8316164472425948</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.99931095376217</v>
+        <v>4.064823205892586</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637088</v>
       </c>
       <c r="C2021" t="n">
         <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.284239526758868</v>
+        <v>-3.233176002454424</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.255922844757056</v>
+        <v>2.276348254478834</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5883251059267368</v>
+        <v>0.7647146421023203</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.922970143330393</v>
+        <v>4.028803865035743</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.795124507020073</v>
+        <v>3.872087403073441</v>
       </c>
       <c r="C2022" t="n">
         <v>3.56505293251054</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.39853977670929</v>
+        <v>-3.429831957716696</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.205280597513077</v>
+        <v>2.192763725110114</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5220329132726447</v>
+        <v>0.7647146421023203</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.878272680474127</v>
+        <v>4.023881717771933</v>
       </c>
     </row>
   </sheetData>
